--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -749,7 +749,11 @@
           <t>ysd-moskva-sayt</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>8365597664</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -903,7 +907,11 @@
           <t>ysd-sankt-peterburg-lending</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>8313753570</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1039,7 +1047,11 @@
           <t>ysd-novosibirsk-magazin</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>8299575117</t>
+        </is>
+      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1331,7 +1343,11 @@
           <t>ysd-nizhniy-novgorod-sayt</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>8299038532</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1485,7 +1501,11 @@
           <t>ysd-chelyabinsk-bot</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>8253641019</t>
+        </is>
+      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1613,7 +1633,11 @@
           <t>ysd-samara-lending</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>8210824952</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1749,7 +1773,11 @@
           <t>ysd-omsk-sayt</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>8271375053</t>
+        </is>
+      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1903,7 +1931,11 @@
           <t>ysd-rostov-na-donu-korp</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>8238494954</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -2477,7 +2509,11 @@
           <t>ysd-perm-magazin</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>8353554171</t>
+        </is>
+      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -2621,7 +2657,11 @@
           <t>ysd-volgograd-lending</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>8271692878</t>
+        </is>
+      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -2757,7 +2797,11 @@
           <t>ysd-krasnodar-sayt</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>8280137941</t>
+        </is>
+      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -2911,7 +2955,11 @@
           <t>ysd-saratov-bot</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>8212507819</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -3316,7 +3364,11 @@
           <t>ysd-izhevsk-sayt</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>8231209173</t>
+        </is>
+      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -3470,7 +3522,11 @@
           <t>ysd-barnaul-korp</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>8290335462</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -3762,7 +3818,11 @@
           <t>ysd-irkutsk-sayt</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>8319873262</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -3916,7 +3976,11 @@
           <t>ysd-habarovsk-lending</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>8310084631</t>
+        </is>
+      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -4198,7 +4262,11 @@
           <t>ysd-vladivostok-sayt</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>8136865868</t>
+        </is>
+      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -4617,7 +4685,11 @@
           <t>ysd-orenburg-sayt</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>8136870531</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -4771,7 +4843,11 @@
           <t>ysd-kemerovo-lending</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>8297936402</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -5044,7 +5120,11 @@
           <t>ysd-ryazan-korp</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>8351848484</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -5622,7 +5702,11 @@
           <t>ysd-kirov-sayt</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>8219544978</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -6045,7 +6129,11 @@
           <t>ysd-kaliningrad-sayt</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>8365002814</t>
+        </is>
+      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -6199,7 +6287,11 @@
           <t>ysd-tula-lending</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>8328983730</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -6631,7 +6723,11 @@
           <t>ysd-stavropol-korp</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>8328905704</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Free</t>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z51"/>
+  <dimension ref="A1:Y51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -579,16 +579,11 @@
           <t>ImageUrls</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>PriceList</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ysd-kazan-sayt</t>
+          <t>8253207537</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -733,15 +728,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -749,11 +735,7 @@
           <t>ysd-moskva-sayt</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>8365597664</t>
-        </is>
-      </c>
+      <c r="B3" s="2" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -891,15 +873,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -907,11 +880,7 @@
           <t>ysd-sankt-peterburg-lending</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>8313753570</t>
-        </is>
-      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1033,13 +1002,6 @@
           <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Лендинг под ключ|8000|Да|за услугу
-Своя услуга|Лендинг на Tilda|10000|Да|за услугу
-Своя услуга|Квиз или калькулятор на лендинг|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1047,11 +1009,7 @@
           <t>ysd-novosibirsk-magazin</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>8299575117</t>
-        </is>
-      </c>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1181,18 +1139,11 @@
           <t>https://ysddev.com/avito/magazin-1.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Интернет-магазин|25000|Да|за услугу
-Своя услуга|Магазин с онлайн-оплатой и доставкой|30000|Да|за услугу
-Своя услуга|Подключение онлайн-оплаты|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ysd-ekaterinburg-korp</t>
+          <t>YSD-004</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1329,13 +1280,6 @@
           <t>https://ysddev.com/avito/korp-1.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Корпоративный сайт до 6 страниц|20000|Да|за услугу
-Своя услуга|Дополнительная страница|3000|Да|за услугу
-Своя услуга|Онлайн-запись или калькулятор|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1343,11 +1287,7 @@
           <t>ysd-nizhniy-novgorod-sayt</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>8299038532</t>
-        </is>
-      </c>
+      <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1485,15 +1425,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1501,11 +1432,7 @@
           <t>ysd-chelyabinsk-bot</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>8253641019</t>
-        </is>
-      </c>
+      <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1619,13 +1546,6 @@
           <t>https://ysddev.com/avito/bot-1.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg</t>
         </is>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Telegram-бот для заявок и записи|8000|Да|за услугу
-Своя услуга|Приём оплаты в боте|5000|Да|за услугу
-Своя услуга|Выгрузка в Google Таблицы или CRM|2000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1633,11 +1553,7 @@
           <t>ysd-samara-lending</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>8210824952</t>
-        </is>
-      </c>
+      <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1759,13 +1675,6 @@
           <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Лендинг под ключ|8000|Да|за услугу
-Своя услуга|Лендинг на Tilda|10000|Да|за услугу
-Своя услуга|Квиз или калькулятор на лендинг|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1773,11 +1682,7 @@
           <t>ysd-omsk-sayt</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>8271375053</t>
-        </is>
-      </c>
+      <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -1915,15 +1820,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1931,11 +1827,7 @@
           <t>ysd-rostov-na-donu-korp</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>8238494954</t>
-        </is>
-      </c>
+      <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -2065,18 +1957,11 @@
           <t>https://ysddev.com/avito/korp-1.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
         </is>
       </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Корпоративный сайт до 6 страниц|20000|Да|за услугу
-Своя услуга|Дополнительная страница|3000|Да|за услугу
-Своя услуга|Онлайн-запись или калькулятор|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ysd-ufa-ai</t>
+          <t>YSD-011</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2196,17 +2081,11 @@
           <t>https://ysddev.com/avito/bot-2.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
         </is>
       </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Чат-бот с нейросетью|15000|Да|за услугу
-Своя услуга|Бот с базой знаний из ваших документов|20000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ysd-krasnoyarsk-figma</t>
+          <t>YSD-012</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2339,13 +2218,6 @@
       <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>https://ysddev.com/avito/figma-1.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Вёрстка страницы из Figma|3000|Да|за услугу
-Своя услуга|Мобильная версия|5000|Да|за услугу
-Своя услуга|Подключение к WordPress|5000|Да|за услугу</t>
         </is>
       </c>
     </row>
@@ -2493,15 +2365,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2509,11 +2372,7 @@
           <t>ysd-perm-magazin</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>8353554171</t>
-        </is>
-      </c>
+      <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -2643,13 +2502,6 @@
           <t>https://ysddev.com/avito/magazin-1.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
         </is>
       </c>
-      <c r="Z15" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Интернет-магазин|25000|Да|за услугу
-Своя услуга|Магазин с онлайн-оплатой и доставкой|30000|Да|за услугу
-Своя услуга|Подключение онлайн-оплаты|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2657,11 +2509,7 @@
           <t>ysd-volgograd-lending</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>8271692878</t>
-        </is>
-      </c>
+      <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -2783,13 +2631,6 @@
           <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Лендинг под ключ|8000|Да|за услугу
-Своя услуга|Лендинг на Tilda|10000|Да|за услугу
-Своя услуга|Квиз или калькулятор на лендинг|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2797,11 +2638,7 @@
           <t>ysd-krasnodar-sayt</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>8280137941</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -2939,15 +2776,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2955,11 +2783,7 @@
           <t>ysd-saratov-bot</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>8212507819</t>
-        </is>
-      </c>
+      <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -3073,18 +2897,11 @@
           <t>https://ysddev.com/avito/bot-1.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
         </is>
       </c>
-      <c r="Z18" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Telegram-бот для заявок и записи|8000|Да|за услугу
-Своя услуга|Приём оплаты в боте|5000|Да|за услугу
-Своя услуга|Выгрузка в Google Таблицы или CRM|2000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ysd-tyumen-lending</t>
+          <t>YSD-018</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -3211,13 +3028,6 @@
       <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Лендинг под ключ|8000|Да|за услугу
-Своя услуга|Лендинг на Tilda|10000|Да|за услугу
-Своя услуга|Квиз или калькулятор на лендинг|5000|Да|за услугу</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3161,6 @@
           <t>https://ysddev.com/avito/vizitka-1.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Дополнительная страница|3000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3364,11 +3168,7 @@
           <t>ysd-izhevsk-sayt</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>8231209173</t>
-        </is>
-      </c>
+      <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -3506,15 +3306,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3522,11 +3313,7 @@
           <t>ysd-barnaul-korp</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>8290335462</t>
-        </is>
-      </c>
+      <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -3656,18 +3443,11 @@
           <t>https://ysddev.com/avito/korp-1.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
-      <c r="Z22" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Корпоративный сайт до 6 страниц|20000|Да|за услугу
-Своя услуга|Дополнительная страница|3000|Да|за услугу
-Своя услуга|Онлайн-запись или калькулятор|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ysd-ulyanovsk-magazin</t>
+          <t>YSD-022</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -3804,13 +3584,6 @@
           <t>https://ysddev.com/avito/magazin-1.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
-      <c r="Z23" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Интернет-магазин|25000|Да|за услугу
-Своя услуга|Магазин с онлайн-оплатой и доставкой|30000|Да|за услугу
-Своя услуга|Подключение онлайн-оплаты|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3818,11 +3591,7 @@
           <t>ysd-irkutsk-sayt</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>8319873262</t>
-        </is>
-      </c>
+      <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -3960,15 +3729,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -3976,11 +3736,7 @@
           <t>ysd-habarovsk-lending</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>8310084631</t>
-        </is>
-      </c>
+      <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -4102,18 +3858,11 @@
           <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Лендинг под ключ|8000|Да|за услугу
-Своя услуга|Лендинг на Tilda|10000|Да|за услугу
-Своя услуга|Квиз или калькулятор на лендинг|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ysd-yaroslavl-dorabotka</t>
+          <t>YSD-024</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -4248,13 +3997,6 @@
           <t>https://ysddev.com/avito/dorabotka-1.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Мелкие правки|2000|Да|за услугу
-Своя услуга|Новая страница|3000|Да|за услугу
-Своя услуга|Ускорение сайта|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4262,11 +4004,7 @@
           <t>ysd-vladivostok-sayt</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>8136865868</t>
-        </is>
-      </c>
+      <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -4404,15 +4142,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4544,12 +4273,6 @@
           <t>https://ysddev.com/avito/vizitka-1.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Дополнительная страница|3000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4671,13 +4394,6 @@
           <t>https://ysddev.com/avito/bot-1.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Telegram-бот для заявок и записи|8000|Да|за услугу
-Своя услуга|Приём оплаты в боте|5000|Да|за услугу
-Своя услуга|Выгрузка в Google Таблицы или CRM|2000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4685,11 +4401,7 @@
           <t>ysd-orenburg-sayt</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>8136870531</t>
-        </is>
-      </c>
+      <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -4827,15 +4539,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4843,11 +4546,7 @@
           <t>ysd-kemerovo-lending</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>8297936402</t>
-        </is>
-      </c>
+      <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -4967,13 +4666,6 @@
       <c r="Y31" s="2" t="inlineStr">
         <is>
           <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
-        </is>
-      </c>
-      <c r="Z31" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Лендинг под ключ|8000|Да|за услугу
-Своя услуга|Лендинг на Tilda|10000|Да|за услугу
-Своя услуга|Квиз или калькулятор на лендинг|5000|Да|за услугу</t>
         </is>
       </c>
     </row>
@@ -5107,12 +4799,6 @@
           <t>https://ysddev.com/avito/vizitka-1.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
-      <c r="Z32" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Дополнительная страница|3000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -5120,11 +4806,7 @@
           <t>ysd-ryazan-korp</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>8351848484</t>
-        </is>
-      </c>
+      <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -5252,13 +4934,6 @@
       <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>https://ysddev.com/avito/korp-1.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
-        </is>
-      </c>
-      <c r="Z33" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Корпоративный сайт до 6 страниц|20000|Да|за услугу
-Своя услуга|Дополнительная страница|3000|Да|за услугу
-Своя услуга|Онлайн-запись или калькулятор|5000|Да|за услугу</t>
         </is>
       </c>
     </row>
@@ -5406,15 +5081,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -5544,13 +5210,6 @@
           <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Лендинг под ключ|8000|Да|за услугу
-Своя услуга|Лендинг на Tilda|10000|Да|за услугу
-Своя услуга|Квиз или калькулятор на лендинг|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -5688,13 +5347,6 @@
           <t>https://ysddev.com/avito/magazin-1.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Интернет-магазин|25000|Да|за услугу
-Своя услуга|Магазин с онлайн-оплатой и доставкой|30000|Да|за услугу
-Своя услуга|Подключение онлайн-оплаты|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -5702,11 +5354,7 @@
           <t>ysd-kirov-sayt</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>8219544978</t>
-        </is>
-      </c>
+      <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -5844,20 +5492,11 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ysd-lipeck-bot</t>
+          <t>YSD-030</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -5976,13 +5615,6 @@
       <c r="Y38" s="2" t="inlineStr">
         <is>
           <t>https://ysddev.com/avito/bot-1.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Telegram-бот для заявок и записи|8000|Да|за услугу
-Своя услуга|Приём оплаты в боте|5000|Да|за услугу
-Своя услуга|Выгрузка в Google Таблицы или CRM|2000|Да|за услугу</t>
         </is>
       </c>
     </row>
@@ -6116,12 +5748,6 @@
           <t>https://ysddev.com/avito/vizitka-1.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Дополнительная страница|3000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -6129,11 +5755,7 @@
           <t>ysd-kaliningrad-sayt</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>8365002814</t>
-        </is>
-      </c>
+      <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -6271,15 +5893,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
-      <c r="Z40" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -6287,11 +5900,7 @@
           <t>ysd-tula-lending</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>8328983730</t>
-        </is>
-      </c>
+      <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -6413,13 +6022,6 @@
           <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Лендинг под ключ|8000|Да|за услугу
-Своя услуга|Лендинг на Tilda|10000|Да|за услугу
-Своя услуга|Квиз или калькулятор на лендинг|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -6553,13 +6155,6 @@
       <c r="Y42" s="2" t="inlineStr">
         <is>
           <t>https://ysddev.com/avito/dorabotka-1.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Мелкие правки|2000|Да|за услугу
-Своя услуга|Новая страница|3000|Да|за услугу
-Своя услуга|Ускорение сайта|5000|Да|за услугу</t>
         </is>
       </c>
     </row>
@@ -6707,15 +6302,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
-      <c r="Z43" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -6723,11 +6309,7 @@
           <t>ysd-stavropol-korp</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>8328905704</t>
-        </is>
-      </c>
+      <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Free</t>
@@ -6855,13 +6437,6 @@
       <c r="Y44" s="2" t="inlineStr">
         <is>
           <t>https://ysddev.com/avito/korp-1.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Корпоративный сайт до 6 страниц|20000|Да|за услугу
-Своя услуга|Дополнительная страница|3000|Да|за услугу
-Своя услуга|Онлайн-запись или калькулятор|5000|Да|за услугу</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6570,6 @@
           <t>https://ysddev.com/avito/vizitka-1.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
-      <c r="Z45" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Дополнительная страница|3000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -7130,13 +6699,6 @@
           <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
-      <c r="Z46" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Лендинг под ключ|8000|Да|за услугу
-Своя услуга|Лендинг на Tilda|10000|Да|за услугу
-Своя услуга|Квиз или калькулятор на лендинг|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -7255,12 +6817,6 @@
       <c r="Y47" s="2" t="inlineStr">
         <is>
           <t>https://ysddev.com/avito/bot-2.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-ai.jpg</t>
-        </is>
-      </c>
-      <c r="Z47" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Чат-бот с нейросетью|15000|Да|за услугу
-Своя услуга|Бот с базой знаний из ваших документов|20000|Да|за услугу</t>
         </is>
       </c>
     </row>
@@ -7408,15 +6964,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
-      <c r="Z48" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -7550,13 +7097,6 @@
       <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>https://ysddev.com/avito/figma-1.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
-        </is>
-      </c>
-      <c r="Z49" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Вёрстка страницы из Figma|3000|Да|за услугу
-Своя услуга|Мобильная версия|5000|Да|за услугу
-Своя услуга|Подключение к WordPress|5000|Да|за услугу</t>
         </is>
       </c>
     </row>
@@ -7704,15 +7244,6 @@
           <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
-      <c r="Z50" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Сайт-визитка|8000|Да|за услугу
-Своя услуга|Сайт на Tilda|10000|Да|за услугу
-Своя услуга|Сайт на WordPress|12000|Да|за услугу
-Своя услуга|Корпоративный сайт|20000|Да|за услугу
-Своя услуга|Интернет-магазин|25000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -7850,13 +7381,6 @@
           <t>https://ysddev.com/avito/magazin-1.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
-      <c r="Z51" s="2" t="inlineStr">
-        <is>
-          <t>Своя услуга|Интернет-магазин|25000|Да|за услугу
-Своя услуга|Магазин с онлайн-оплатой и доставкой|30000|Да|за услугу
-Своя услуга|Подключение онлайн-оплаты|5000|Да|за услугу</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -696,9 +696,10 @@
           <t>Делаю сайты и ботов для бизнеса в Казани и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -714,18 +715,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -841,9 +842,10 @@
           <t>Работаю с заказчиками в Москве онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -859,18 +861,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -976,7 +978,7 @@
       <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Санкт-Петербурге: без офиса и менеджеров, напрямую с разработчиком.
-Одностраничный сайт под одну услугу, который собирает заявки. От 8 000 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -988,18 +990,18 @@
 Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене.
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
 Расскажите, что продаёте и кому — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1115,7 @@
       <c r="W5" s="2" t="inlineStr">
         <is>
           <t>В Новосибирске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Магазин, в котором покупают, а не бросают корзину. От 25 000 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 30 000 ₽.
+Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -1123,20 +1125,20 @@
 Админка: товары, цены, остатки, заказы
 Уведомления о заказах в Telegram
 60 дней правок после сдачи
-Интеграции с 1С, МойСклад, CRM и службами доставки — от 5 000 ₽.
+Интеграции с 1С, МойСклад, CRM и службами доставки — от 3 000 ₽.
 Напишите, чем торгуете и сколько позиций — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1n.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1256,7 @@
       <c r="W6" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Екатеринбурге и по всей России, удалённо.
-Многостраничный сайт компании — 20 000 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -1264,20 +1266,20 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно по прайсу те же работы стоят 25 000 ₽, пакетом — 20 000 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1n.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -1393,9 +1395,10 @@
           <t>Работаю с заказчиками в Нижнем Новгороде онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -1411,18 +1414,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1523,7 @@
       <c r="W8" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Челябинске: без офиса и менеджеров, напрямую с разработчиком.
-Бот, который принимает заявки, пока вы заняты. 8 000 ₽, срок 1–2 дня.
+Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -1532,18 +1535,18 @@
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до начала работы. Исходный код и доступы — ваши.
 Напишите, что бот должен делать — примеры покажу в переписке.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg</t>
+          <t>https://ysddev.com/avito/bot-1n.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1652,7 @@
       <c r="W9" s="2" t="inlineStr">
         <is>
           <t>В Самаре работаю удалённо — встречи не нужны, всё решаем в переписке.
-Одностраничный сайт под одну услугу, который собирает заявки. От 8 000 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -1661,18 +1664,18 @@
 Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене.
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
 Расскажите, что продаёте и кому — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -1788,9 +1791,10 @@
           <t>Делаю сайты и ботов для бизнеса в Омске и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -1806,18 +1810,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1935,7 @@
       <c r="W11" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Ростове-на-Дону онлайн: смета и срок — в первый день.
-Многостраничный сайт компании — 20 000 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -1941,20 +1945,20 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно по прайсу те же работы стоят 25 000 ₽, пакетом — 20 000 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
+          <t>https://ysddev.com/avito/korp-1n.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2060,7 @@
       <c r="W12" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Уфе: без офиса и менеджеров, напрямую с разработчиком.
-Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 15 000 ₽.
+Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 9 990 ₽.
 В ЧЁМ РАЗНИЦА
 Обычный бот ведёт по кнопкам и теряет человека на первом вопросе не по сценарию. Бот с ИИ понимает вопрос словами и отвечает по вашим данным.
 ЧТО ДЕЛАЮ
@@ -2067,18 +2071,18 @@
 Лимиты, чтобы бот не тратил лишнего
 Работающий пример покажу до оплаты.
 Опишите, на какие вопросы он должен отвечать.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-2.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
+          <t>https://ysddev.com/avito/bot-2n.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2200,7 @@
       <c r="W13" s="2" t="inlineStr">
         <is>
           <t>В Красноярске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Есть макет — сверстаю. От 3 000 ₽ за страницу, от 1 дня.
+Есть макет — сверстаю. От 2 490 ₽ за страницу, от 1 дня.
 КАК ВЕРСТАЮ
 Пиксель в пиксель по макету
 Адаптив: телефон, планшет, компьютер
@@ -2206,18 +2210,18 @@
 Проверяю в Chrome, Safari, Firefox и на телефонах
 Если нужно — подключу к CMS, выложу на хостинг, настрою домен.
 Пришлите ссылку на макет — назову цену и срок в тот же день.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/figma-1.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/figma-1n.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -2333,9 +2337,10 @@
           <t>Делаю сайты и ботов для бизнеса в Воронеже и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -2351,18 +2356,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2481,7 @@
       <c r="W15" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Перми онлайн: смета и срок — в первый день.
-Магазин, в котором покупают, а не бросают корзину. От 25 000 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 30 000 ₽.
+Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -2486,20 +2491,20 @@
 Админка: товары, цены, остатки, заказы
 Уведомления о заказах в Telegram
 60 дней правок после сдачи
-Интеграции с 1С, МойСклад, CRM и службами доставки — от 5 000 ₽.
+Интеграции с 1С, МойСклад, CRM и службами доставки — от 3 000 ₽.
 Напишите, чем торгуете и сколько позиций — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1n.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2610,7 @@
       <c r="W16" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Волгограде: без офиса и менеджеров, напрямую с разработчиком.
-Одностраничный сайт под одну услугу, который собирает заявки. От 8 000 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -2617,18 +2622,18 @@
 Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене.
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
 Расскажите, что продаёте и кому — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -2744,9 +2749,10 @@
           <t>В Краснодаре работаю удалённо — встречи не нужны, всё решаем в переписке.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -2762,18 +2768,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2877,7 @@
       <c r="W18" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Саратове и по всей России, удалённо.
-Бот, который принимает заявки, пока вы заняты. 8 000 ₽, срок 1–2 дня.
+Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -2883,18 +2889,18 @@
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до начала работы. Исходный код и доступы — ваши.
 Напишите, что бот должен делать — примеры покажу в переписке.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
+          <t>https://ysddev.com/avito/bot-1n.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3010,7 @@
       <c r="W19" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Тюмени онлайн: смета и срок — в первый день.
-Одностраничный сайт под одну услугу, который собирает заявки. От 8 000 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -3016,18 +3022,18 @@
 Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене.
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
 Расскажите, что продаёте и кому — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3139,7 @@
       <c r="W20" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Тольятти: без офиса и менеджеров, напрямую с разработчиком.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 8 000 ₽, 2–4 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -3147,18 +3153,18 @@
 Покажу, как менять тексты самому
 Макет — до оплаты. 14 дней правок бесплатно.
 Напишите, чем занимаетесь — пришлю пример и точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1n.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -3274,9 +3280,10 @@
           <t>В Ижевске работаю удалённо — встречи не нужны, всё решаем в переписке.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -3292,18 +3299,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3424,7 @@
       <c r="W22" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Барнауле и по всей России, удалённо.
-Многостраничный сайт компании — 20 000 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -3427,20 +3434,20 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно по прайсу те же работы стоят 25 000 ₽, пакетом — 20 000 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/korp-1n.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3565,7 @@
       <c r="W23" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Ульяновске онлайн: смета и срок — в первый день.
-Магазин, в котором покупают, а не бросают корзину. От 25 000 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 30 000 ₽.
+Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -3568,20 +3575,20 @@
 Админка: товары, цены, остатки, заказы
 Уведомления о заказах в Telegram
 60 дней правок после сдачи
-Интеграции с 1С, МойСклад, CRM и службами доставки — от 5 000 ₽.
+Интеграции с 1С, МойСклад, CRM и службами доставки — от 3 000 ₽.
 Напишите, чем торгуете и сколько позиций — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1n.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
     </row>
@@ -3697,9 +3704,10 @@
           <t>Для бизнеса в Иркутске: без офиса и менеджеров, напрямую с разработчиком.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -3715,18 +3723,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3840,7 @@
       <c r="W25" s="2" t="inlineStr">
         <is>
           <t>В Хабаровске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Одностраничный сайт под одну услугу, который собирает заявки. От 8 000 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -3844,18 +3852,18 @@
 Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене.
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
 Расскажите, что продаёте и кому — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
+          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3981,7 @@
       <c r="W26" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Ярославле и по всей России, удалённо.
-Сайт уже есть, но что-то не так — разберусь и починю. От 2 000 ₽, от 1 дня.
+Сайт уже есть, но что-то не так — разберусь и починю. От 1 000 ₽, от 1 дня.
 С ЧЕМ ПРИХОДЯТ
 Нужны новые страницы или разделы
 Форма заявки не отправляется
@@ -3983,18 +3991,18 @@
 Дизайн устарел
 Работаю с WordPress, Tilda, Битрикс и сайтами на коде, чужой код беру. Смотрю сайт и говорю прямо: что чинится за час, а что дешевле сделать заново.
 Оценка бесплатная. Дайте ссылку на сайт и напишите, что не устраивает.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/dorabotka-1.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/dorabotka-1n.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -4110,9 +4118,10 @@
           <t>Работаю с заказчиками во Владивостоке онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -4128,18 +4137,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4254,7 @@
       <c r="W28" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Махачкале: без офиса и менеджеров, напрямую с разработчиком.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 8 000 ₽, 2–4 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -4259,18 +4268,18 @@
 Покажу, как менять тексты самому
 Макет — до оплаты. 14 дней правок бесплатно.
 Напишите, чем занимаетесь — пришлю пример и точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1n.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4377,7 @@
       <c r="W29" s="2" t="inlineStr">
         <is>
           <t>В Томске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Бот, который принимает заявки, пока вы заняты. 8 000 ₽, срок 1–2 дня.
+Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -4380,18 +4389,18 @@
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до начала работы. Исходный код и доступы — ваши.
 Напишите, что бот должен делать — примеры покажу в переписке.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg</t>
+          <t>https://ysddev.com/avito/bot-1n.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -4507,9 +4516,10 @@
           <t>Делаю сайты и ботов для бизнеса в Оренбурге и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -4525,18 +4535,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4652,7 @@
       <c r="W31" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Кемерово онлайн: смета и срок — в первый день.
-Одностраничный сайт под одну услугу, который собирает заявки. От 8 000 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -4654,18 +4664,18 @@
 Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене.
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
 Расскажите, что продаёте и кому — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4781,7 @@
       <c r="W32" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Новокузнецке: без офиса и менеджеров, напрямую с разработчиком.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 8 000 ₽, 2–4 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -4785,18 +4795,18 @@
 Покажу, как менять тексты самому
 Макет — до оплаты. 14 дней правок бесплатно.
 Напишите, чем занимаетесь — пришлю пример и точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1n.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4920,7 @@
       <c r="W33" s="2" t="inlineStr">
         <is>
           <t>В Рязани работаю удалённо — встречи не нужны, всё решаем в переписке.
-Многостраничный сайт компании — 20 000 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -4920,20 +4930,20 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно по прайсу те же работы стоят 25 000 ₽, пакетом — 20 000 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/korp-1n.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -5049,9 +5059,10 @@
           <t>Делаю сайты и ботов для бизнеса в Набережных Челнах и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -5067,18 +5078,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5195,7 @@
       <c r="W35" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Астрахани онлайн: смета и срок — в первый день.
-Одностраничный сайт под одну услугу, который собирает заявки. От 8 000 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -5196,18 +5207,18 @@
 Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене.
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
 Расскажите, что продаёте и кому — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5332,7 @@
       <c r="W36" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Пензе: без офиса и менеджеров, напрямую с разработчиком.
-Магазин, в котором покупают, а не бросают корзину. От 25 000 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 30 000 ₽.
+Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -5331,20 +5342,20 @@
 Админка: товары, цены, остатки, заказы
 Уведомления о заказах в Telegram
 60 дней правок после сдачи
-Интеграции с 1С, МойСклад, CRM и службами доставки — от 5 000 ₽.
+Интеграции с 1С, МойСклад, CRM и службами доставки — от 3 000 ₽.
 Напишите, чем торгуете и сколько позиций — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1n.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg</t>
         </is>
       </c>
     </row>
@@ -5460,9 +5471,10 @@
           <t>В Кирове работаю удалённо — встречи не нужны, всё решаем в переписке.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -5478,18 +5490,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5603,7 @@
       <c r="W38" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Липецке и по всей России, удалённо.
-Бот, который принимает заявки, пока вы заняты. 8 000 ₽, срок 1–2 дня.
+Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -5603,18 +5615,18 @@
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до начала работы. Исходный код и доступы — ваши.
 Напишите, что бот должен делать — примеры покажу в переписке.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg</t>
+          <t>https://ysddev.com/avito/bot-1n.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5732,7 @@
       <c r="W39" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Чебоксарах онлайн: смета и срок — в первый день.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 8 000 ₽, 2–4 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -5734,18 +5746,18 @@
 Покажу, как менять тексты самому
 Макет — до оплаты. 14 дней правок бесплатно.
 Напишите, чем занимаетесь — пришлю пример и точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1n.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -5861,9 +5873,10 @@
           <t>Для бизнеса в Калининграде: без офиса и менеджеров, напрямую с разработчиком.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -5879,18 +5892,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -5996,7 +6009,7 @@
       <c r="W41" s="2" t="inlineStr">
         <is>
           <t>В Туле работаю удалённо — встречи не нужны, всё решаем в переписке.
-Одностраничный сайт под одну услугу, который собирает заявки. От 8 000 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -6008,18 +6021,18 @@
 Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене.
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
 Расскажите, что продаёте и кому — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6146,7 @@
       <c r="W42" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Курске и по всей России, удалённо.
-Сайт уже есть, но что-то не так — разберусь и починю. От 2 000 ₽, от 1 дня.
+Сайт уже есть, но что-то не так — разберусь и починю. От 1 000 ₽, от 1 дня.
 С ЧЕМ ПРИХОДЯТ
 Нужны новые страницы или разделы
 Форма заявки не отправляется
@@ -6143,18 +6156,18 @@
 Дизайн устарел
 Работаю с WordPress, Tilda, Битрикс и сайтами на коде, чужой код беру. Смотрю сайт и говорю прямо: что чинится за час, а что дешевле сделать заново.
 Оценка бесплатная. Дайте ссылку на сайт и напишите, что не устраивает.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/dorabotka-1.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/dorabotka-1n.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -6270,9 +6283,10 @@
           <t>Работаю с заказчиками в Сочи онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -6288,18 +6302,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6427,7 @@
       <c r="W44" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Ставрополе: без офиса и менеджеров, напрямую с разработчиком.
-Многостраничный сайт компании — 20 000 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -6423,20 +6437,20 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно по прайсу те же работы стоят 25 000 ₽, пакетом — 20 000 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1n.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6556,7 @@
       <c r="W45" s="2" t="inlineStr">
         <is>
           <t>В Улан-Удэ работаю удалённо — встречи не нужны, всё решаем в переписке.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 8 000 ₽, 2–4 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -6556,18 +6570,18 @@
 Покажу, как менять тексты самому
 Макет — до оплаты. 14 дней правок бесплатно.
 Напишите, чем занимаетесь — пришлю пример и точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1n.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6687,7 @@
       <c r="W46" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Твери и по всей России, удалённо.
-Одностраничный сайт под одну услугу, который собирает заявки. От 8 000 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -6685,18 +6699,18 @@
 Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене.
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
 Расскажите, что продаёте и кому — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -6794,7 +6808,7 @@
       <c r="W47" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Магнитогорске онлайн: смета и срок — в первый день.
-Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 15 000 ₽.
+Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 9 990 ₽.
 В ЧЁМ РАЗНИЦА
 Обычный бот ведёт по кнопкам и теряет человека на первом вопросе не по сценарию. Бот с ИИ понимает вопрос словами и отвечает по вашим данным.
 ЧТО ДЕЛАЮ
@@ -6805,18 +6819,18 @@
 Лимиты, чтобы бот не тратил лишнего
 Работающий пример покажу до оплаты.
 Опишите, на какие вопросы он должен отвечать.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-2.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-ai.jpg</t>
+          <t>https://ysddev.com/avito/bot-2n.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-ai.jpg</t>
         </is>
       </c>
     </row>
@@ -6932,9 +6946,10 @@
           <t>Для бизнеса в Иванове: без офиса и менеджеров, напрямую с разработчиком.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -6950,18 +6965,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7090,7 @@
       <c r="W49" s="2" t="inlineStr">
         <is>
           <t>В Брянске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Есть макет — сверстаю. От 3 000 ₽ за страницу, от 1 дня.
+Есть макет — сверстаю. От 2 490 ₽ за страницу, от 1 дня.
 КАК ВЕРСТАЮ
 Пиксель в пиксель по макету
 Адаптив: телефон, планшет, компьютер
@@ -7085,18 +7100,18 @@
 Проверяю в Chrome, Safari, Firefox и на телефонах
 Если нужно — подключу к CMS, выложу на хостинг, настрою домен.
 Пришлите ссылку на макет — назову цену и срок в тот же день.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/figma-1.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/figma-1n.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -7212,9 +7227,10 @@
           <t>Делаю сайты и ботов для бизнеса в Белгороде и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 8 000 ₽, 2–4 дня
-Многостраничный сайт — 20 000 ₽, 5–8 дней
-Интернет-магазин — от 25 000 ₽, 10–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
 ЧТО ВХОДИТ
 Структура и дизайн под вашу задачу, не шаблон
@@ -7230,18 +7246,18 @@
 14 дней правок после сдачи бесплатно
 Исходники, доступы и домен остаются у вас
 Напишите, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7371,7 @@
       <c r="W51" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками во Владимире онлайн: смета и срок — в первый день.
-Магазин, в котором покупают, а не бросают корзину. От 25 000 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 30 000 ₽.
+Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -7365,20 +7381,20 @@
 Админка: товары, цены, остатки, заказы
 Уведомления о заказах в Telegram
 60 дней правок после сдачи
-Интеграции с 1С, МойСклад, CRM и службами доставки — от 5 000 ₽.
+Интеграции с 1С, МойСклад, CRM и службами доставки — от 3 000 ₽.
 Напишите, чем торгуете и сколько позиций — посчитаю точно.
-Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже.
+Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1n.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -696,13 +696,14 @@
           <t>Делаю сайты и ботов для бизнеса в Казани и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -721,12 +722,12 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -842,13 +843,14 @@
           <t>Работаю с заказчиками в Москве онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -867,12 +869,12 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -978,7 +980,9 @@
       <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Санкт-Петербурге: без офиса и менеджеров, напрямую с разработчиком.
-Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки.
+Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
+С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -996,12 +1000,12 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1119,7 @@
       <c r="W5" s="2" t="inlineStr">
         <is>
           <t>В Новосибирске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
+Магазин, в котором покупают, а не бросают корзину. До 50 товаров, заказы приходят вам в Telegram — 14 990 ₽, 7–10 дней. С онлайн-оплатой и расчётом доставки — 19 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -1133,12 +1137,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1n.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1s.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1260,7 @@
       <c r="W6" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Екатеринбурге и по всей России, удалённо.
-Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании: до 4 страниц — 9 990 ₽, до 6 страниц с онлайн-записью или калькулятором — 14 990 ₽. Срок 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -1266,7 +1270,7 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — от 9 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
 Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
@@ -1274,12 +1278,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1n.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1s.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -1395,13 +1399,14 @@
           <t>Работаю с заказчиками в Нижнем Новгороде онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -1420,12 +1425,12 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1528,9 @@
       <c r="W8" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Челябинске: без офиса и менеджеров, напрямую с разработчиком.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
+Бот, который принимает заявки, пока вы заняты.
+Старт — 2 990 ₽, 1 день: бот-визитка с меню, ответами на частые вопросы и приёмом заявок вам в личку.
+Запись, оплата, выгрузка в таблицы — от 4 990 ₽, 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -1541,12 +1548,12 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1n.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg</t>
+          <t>https://ysddev.com/avito/bot-1s.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1659,9 @@
       <c r="W9" s="2" t="inlineStr">
         <is>
           <t>В Самаре работаю удалённо — встречи не нужны, всё решаем в переписке.
-Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки.
+Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
+С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -1670,12 +1679,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -1791,13 +1800,14 @@
           <t>Делаю сайты и ботов для бизнеса в Омске и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -1816,12 +1826,12 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1945,7 @@
       <c r="W11" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Ростове-на-Дону онлайн: смета и срок — в первый день.
-Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании: до 4 страниц — 9 990 ₽, до 6 страниц с онлайн-записью или калькулятором — 14 990 ₽. Срок 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -1945,7 +1955,7 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — от 9 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
 Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
@@ -1953,12 +1963,12 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1n.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
+          <t>https://ysddev.com/avito/korp-1s.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2070,7 @@
       <c r="W12" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Уфе: без офиса и менеджеров, напрямую с разработчиком.
-Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 9 990 ₽.
+Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 7 990 ₽.
 В ЧЁМ РАЗНИЦА
 Обычный бот ведёт по кнопкам и теряет человека на первом вопросе не по сценарию. Бот с ИИ понимает вопрос словами и отвечает по вашим данным.
 ЧТО ДЕЛАЮ
@@ -2077,12 +2087,12 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-2n.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
+          <t>https://ysddev.com/avito/bot-2s.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2210,7 @@
       <c r="W13" s="2" t="inlineStr">
         <is>
           <t>В Красноярске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Есть макет — сверстаю. От 2 490 ₽ за страницу, от 1 дня.
+Есть макет — сверстаю. От 1 990 ₽ за страницу, от 1 дня.
 КАК ВЕРСТАЮ
 Пиксель в пиксель по макету
 Адаптив: телефон, планшет, компьютер
@@ -2216,12 +2226,12 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/figma-1n.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/figma-1s.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -2337,13 +2347,14 @@
           <t>Делаю сайты и ботов для бизнеса в Воронеже и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -2362,12 +2373,12 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2492,7 @@
       <c r="W15" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Перми онлайн: смета и срок — в первый день.
-Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
+Магазин, в котором покупают, а не бросают корзину. До 50 товаров, заказы приходят вам в Telegram — 14 990 ₽, 7–10 дней. С онлайн-оплатой и расчётом доставки — 19 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -2499,12 +2510,12 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1n.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1s.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2621,9 @@
       <c r="W16" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Волгограде: без офиса и менеджеров, напрямую с разработчиком.
-Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки.
+Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
+С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -2628,12 +2641,12 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -2749,13 +2762,14 @@
           <t>В Краснодаре работаю удалённо — встречи не нужны, всё решаем в переписке.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -2774,12 +2788,12 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2891,9 @@
       <c r="W18" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Саратове и по всей России, удалённо.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
+Бот, который принимает заявки, пока вы заняты.
+Старт — 2 990 ₽, 1 день: бот-визитка с меню, ответами на частые вопросы и приёмом заявок вам в личку.
+Запись, оплата, выгрузка в таблицы — от 4 990 ₽, 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -2895,12 +2911,12 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1n.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
+          <t>https://ysddev.com/avito/bot-1s.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3026,9 @@
       <c r="W19" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Тюмени онлайн: смета и срок — в первый день.
-Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки.
+Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
+С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -3028,12 +3046,12 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3157,9 @@
       <c r="W20" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Тольятти: без офиса и менеджеров, напрямую с разработчиком.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит.
+Старт — 2 990 ₽, 1 день: одна страница на готовой структуре с вашими текстами и фото.
+Со своим дизайном и до 3 страниц — 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -3159,12 +3179,12 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1n.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1s.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -3280,13 +3300,14 @@
           <t>В Ижевске работаю удалённо — встречи не нужны, всё решаем в переписке.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -3305,12 +3326,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3445,7 @@
       <c r="W22" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Барнауле и по всей России, удалённо.
-Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании: до 4 страниц — 9 990 ₽, до 6 страниц с онлайн-записью или калькулятором — 14 990 ₽. Срок 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -3434,7 +3455,7 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — от 9 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
 Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
@@ -3442,12 +3463,12 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1n.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/korp-1s.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3586,7 @@
       <c r="W23" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Ульяновске онлайн: смета и срок — в первый день.
-Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
+Магазин, в котором покупают, а не бросают корзину. До 50 товаров, заказы приходят вам в Telegram — 14 990 ₽, 7–10 дней. С онлайн-оплатой и расчётом доставки — 19 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -3583,12 +3604,12 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1n.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1s.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
     </row>
@@ -3704,13 +3725,14 @@
           <t>Для бизнеса в Иркутске: без офиса и менеджеров, напрямую с разработчиком.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -3729,12 +3751,12 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3862,9 @@
       <c r="W25" s="2" t="inlineStr">
         <is>
           <t>В Хабаровске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки.
+Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
+С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -3858,12 +3882,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
+          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
     </row>
@@ -3981,7 +4005,7 @@
       <c r="W26" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Ярославле и по всей России, удалённо.
-Сайт уже есть, но что-то не так — разберусь и починю. От 1 000 ₽, от 1 дня.
+Сайт уже есть, но что-то не так — разберусь и починю. Мелкая правка — от 500 ₽, в тот же день.
 С ЧЕМ ПРИХОДЯТ
 Нужны новые страницы или разделы
 Форма заявки не отправляется
@@ -3997,12 +4021,12 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>500</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/dorabotka-1n.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/dorabotka-1s.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -4118,13 +4142,14 @@
           <t>Работаю с заказчиками во Владивостоке онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -4143,12 +4168,12 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4279,9 @@
       <c r="W28" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Махачкале: без офиса и менеджеров, напрямую с разработчиком.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит.
+Старт — 2 990 ₽, 1 день: одна страница на готовой структуре с вашими текстами и фото.
+Со своим дизайном и до 3 страниц — 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -4274,12 +4301,12 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1n.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1s.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4404,9 @@
       <c r="W29" s="2" t="inlineStr">
         <is>
           <t>В Томске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
+Бот, который принимает заявки, пока вы заняты.
+Старт — 2 990 ₽, 1 день: бот-визитка с меню, ответами на частые вопросы и приёмом заявок вам в личку.
+Запись, оплата, выгрузка в таблицы — от 4 990 ₽, 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -4395,12 +4424,12 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1n.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg</t>
+          <t>https://ysddev.com/avito/bot-1s.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -4516,13 +4545,14 @@
           <t>Делаю сайты и ботов для бизнеса в Оренбурге и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -4541,12 +4571,12 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4682,9 @@
       <c r="W31" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Кемерово онлайн: смета и срок — в первый день.
-Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки.
+Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
+С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -4670,12 +4702,12 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4813,9 @@
       <c r="W32" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Новокузнецке: без офиса и менеджеров, напрямую с разработчиком.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит.
+Старт — 2 990 ₽, 1 день: одна страница на готовой структуре с вашими текстами и фото.
+Со своим дизайном и до 3 страниц — 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -4801,12 +4835,12 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1n.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1s.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4954,7 @@
       <c r="W33" s="2" t="inlineStr">
         <is>
           <t>В Рязани работаю удалённо — встречи не нужны, всё решаем в переписке.
-Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании: до 4 страниц — 9 990 ₽, до 6 страниц с онлайн-записью или калькулятором — 14 990 ₽. Срок 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -4930,7 +4964,7 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — от 9 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
 Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
@@ -4938,12 +4972,12 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1n.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/korp-1s.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -5059,13 +5093,14 @@
           <t>Делаю сайты и ботов для бизнеса в Набережных Челнах и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -5084,12 +5119,12 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5230,9 @@
       <c r="W35" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Астрахани онлайн: смета и срок — в первый день.
-Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки.
+Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
+С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -5213,12 +5250,12 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5369,7 @@
       <c r="W36" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Пензе: без офиса и менеджеров, напрямую с разработчиком.
-Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
+Магазин, в котором покупают, а не бросают корзину. До 50 товаров, заказы приходят вам в Telegram — 14 990 ₽, 7–10 дней. С онлайн-оплатой и расчётом доставки — 19 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -5350,12 +5387,12 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1n.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1s.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5508,14 @@
           <t>В Кирове работаю удалённо — встречи не нужны, всё решаем в переписке.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -5496,12 +5534,12 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5641,9 @@
       <c r="W38" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Липецке и по всей России, удалённо.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
+Бот, который принимает заявки, пока вы заняты.
+Старт — 2 990 ₽, 1 день: бот-визитка с меню, ответами на частые вопросы и приёмом заявок вам в личку.
+Запись, оплата, выгрузка в таблицы — от 4 990 ₽, 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -5621,12 +5661,12 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1n.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg</t>
+          <t>https://ysddev.com/avito/bot-1s.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5772,9 @@
       <c r="W39" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Чебоксарах онлайн: смета и срок — в первый день.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит.
+Старт — 2 990 ₽, 1 день: одна страница на готовой структуре с вашими текстами и фото.
+Со своим дизайном и до 3 страниц — 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -5752,12 +5794,12 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1n.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1s.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -5873,13 +5915,14 @@
           <t>Для бизнеса в Калининграде: без офиса и менеджеров, напрямую с разработчиком.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -5898,12 +5941,12 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6052,9 @@
       <c r="W41" s="2" t="inlineStr">
         <is>
           <t>В Туле работаю удалённо — встречи не нужны, всё решаем в переписке.
-Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки.
+Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
+С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -6027,12 +6072,12 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6191,7 @@
       <c r="W42" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Курске и по всей России, удалённо.
-Сайт уже есть, но что-то не так — разберусь и починю. От 1 000 ₽, от 1 дня.
+Сайт уже есть, но что-то не так — разберусь и починю. Мелкая правка — от 500 ₽, в тот же день.
 С ЧЕМ ПРИХОДЯТ
 Нужны новые страницы или разделы
 Форма заявки не отправляется
@@ -6162,12 +6207,12 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>500</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/dorabotka-1n.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/dorabotka-1s.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -6283,13 +6328,14 @@
           <t>Работаю с заказчиками в Сочи онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -6308,12 +6354,12 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6473,7 @@
       <c r="W44" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Ставрополе: без офиса и менеджеров, напрямую с разработчиком.
-Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании: до 4 страниц — 9 990 ₽, до 6 страниц с онлайн-записью или калькулятором — 14 990 ₽. Срок 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -6437,7 +6483,7 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — от 9 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
 Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
@@ -6445,12 +6491,12 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1n.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1s.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6602,9 @@
       <c r="W45" s="2" t="inlineStr">
         <is>
           <t>В Улан-Удэ работаю удалённо — встречи не нужны, всё решаем в переписке.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит.
+Старт — 2 990 ₽, 1 день: одна страница на готовой структуре с вашими текстами и фото.
+Со своим дизайном и до 3 страниц — 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -6576,12 +6624,12 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1n.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1s.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6735,9 @@
       <c r="W46" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Твери и по всей России, удалённо.
-Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки.
+Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
+С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -6705,12 +6755,12 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1n.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6858,7 @@
       <c r="W47" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Магнитогорске онлайн: смета и срок — в первый день.
-Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 9 990 ₽.
+Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 7 990 ₽.
 В ЧЁМ РАЗНИЦА
 Обычный бот ведёт по кнопкам и теряет человека на первом вопросе не по сценарию. Бот с ИИ понимает вопрос словами и отвечает по вашим данным.
 ЧТО ДЕЛАЮ
@@ -6825,12 +6875,12 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-2n.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-ai.jpg</t>
+          <t>https://ysddev.com/avito/bot-2s.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-ai.jpg</t>
         </is>
       </c>
     </row>
@@ -6946,13 +6996,14 @@
           <t>Для бизнеса в Иванове: без офиса и менеджеров, напрямую с разработчиком.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -6971,12 +7022,12 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7141,7 @@
       <c r="W49" s="2" t="inlineStr">
         <is>
           <t>В Брянске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Есть макет — сверстаю. От 2 490 ₽ за страницу, от 1 дня.
+Есть макет — сверстаю. От 1 990 ₽ за страницу, от 1 дня.
 КАК ВЕРСТАЮ
 Пиксель в пиксель по макету
 Адаптив: телефон, планшет, компьютер
@@ -7106,12 +7157,12 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/figma-1n.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/figma-1s.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -7227,13 +7278,14 @@
           <t>Делаю сайты и ботов для бизнеса в Белгороде и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Сайт-визитка — от 4 990 ₽, 2–3 дня
-Лендинг — от 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 14 990 ₽, 5–8 дней
-Интернет-магазин — от 19 990 ₽, 10–14 дней
+Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
+Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
+Лендинг под рекламу — 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 9 990 ₽, 5–8 дней
+Интернет-магазин — от 14 990 ₽, 7–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
+ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
+Структура под вашу задачу
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -7252,12 +7304,12 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1n.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7423,7 @@
       <c r="W51" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками во Владимире онлайн: смета и срок — в первый день.
-Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
+Магазин, в котором покупают, а не бросают корзину. До 50 товаров, заказы приходят вам в Telegram — 14 990 ₽, 7–10 дней. С онлайн-оплатой и расчётом доставки — 19 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -7389,12 +7441,12 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1n.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1s.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -696,14 +696,13 @@
           <t>Делаю сайты и ботов для бизнеса в Казани и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -722,12 +721,12 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -843,14 +842,13 @@
           <t>Работаю с заказчиками в Москве онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -869,12 +867,12 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -980,9 +978,7 @@
       <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Санкт-Петербурге: без офиса и менеджеров, напрямую с разработчиком.
-Одностраничный сайт под одну услугу, который собирает заявки.
-Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
-С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -1000,12 +996,12 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1115,7 @@
       <c r="W5" s="2" t="inlineStr">
         <is>
           <t>В Новосибирске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Магазин, в котором покупают, а не бросают корзину. До 50 товаров, заказы приходят вам в Telegram — 14 990 ₽, 7–10 дней. С онлайн-оплатой и расчётом доставки — 19 990 ₽.
+Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -1137,12 +1133,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1s.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1256,7 @@
       <c r="W6" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Екатеринбурге и по всей России, удалённо.
-Многостраничный сайт компании: до 4 страниц — 9 990 ₽, до 6 страниц с онлайн-записью или калькулятором — 14 990 ₽. Срок 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -1270,7 +1266,7 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно те же работы стоят около 20 000 ₽, пакетом — от 9 990 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
 Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
@@ -1278,12 +1274,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1s.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -1399,14 +1395,13 @@
           <t>Работаю с заказчиками в Нижнем Новгороде онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -1425,12 +1420,12 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -1528,9 +1523,7 @@
       <c r="W8" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Челябинске: без офиса и менеджеров, напрямую с разработчиком.
-Бот, который принимает заявки, пока вы заняты.
-Старт — 2 990 ₽, 1 день: бот-визитка с меню, ответами на частые вопросы и приёмом заявок вам в личку.
-Запись, оплата, выгрузка в таблицы — от 4 990 ₽, 1–2 дня.
+Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -1548,12 +1541,12 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1s.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg</t>
+          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg</t>
         </is>
       </c>
     </row>
@@ -1659,9 +1652,7 @@
       <c r="W9" s="2" t="inlineStr">
         <is>
           <t>В Самаре работаю удалённо — встречи не нужны, всё решаем в переписке.
-Одностраничный сайт под одну услугу, который собирает заявки.
-Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
-С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -1679,12 +1670,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -1800,14 +1791,13 @@
           <t>Делаю сайты и ботов для бизнеса в Омске и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -1826,12 +1816,12 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1935,7 @@
       <c r="W11" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Ростове-на-Дону онлайн: смета и срок — в первый день.
-Многостраничный сайт компании: до 4 страниц — 9 990 ₽, до 6 страниц с онлайн-записью или калькулятором — 14 990 ₽. Срок 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -1955,7 +1945,7 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно те же работы стоят около 20 000 ₽, пакетом — от 9 990 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
 Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
@@ -1963,12 +1953,12 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1s.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
+          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2060,7 @@
       <c r="W12" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Уфе: без офиса и менеджеров, напрямую с разработчиком.
-Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 7 990 ₽.
+Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 9 990 ₽.
 В ЧЁМ РАЗНИЦА
 Обычный бот ведёт по кнопкам и теряет человека на первом вопросе не по сценарию. Бот с ИИ понимает вопрос словами и отвечает по вашим данным.
 ЧТО ДЕЛАЮ
@@ -2087,12 +2077,12 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-2s.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
+          <t>https://ysddev.com/avito/bot-2h.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2200,7 @@
       <c r="W13" s="2" t="inlineStr">
         <is>
           <t>В Красноярске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Есть макет — сверстаю. От 1 990 ₽ за страницу, от 1 дня.
+Есть макет — сверстаю. От 2 490 ₽ за страницу, от 1 дня.
 КАК ВЕРСТАЮ
 Пиксель в пиксель по макету
 Адаптив: телефон, планшет, компьютер
@@ -2226,12 +2216,12 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/figma-1s.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/figma-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -2347,14 +2337,13 @@
           <t>Делаю сайты и ботов для бизнеса в Воронеже и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -2373,12 +2362,12 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2481,7 @@
       <c r="W15" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Перми онлайн: смета и срок — в первый день.
-Магазин, в котором покупают, а не бросают корзину. До 50 товаров, заказы приходят вам в Telegram — 14 990 ₽, 7–10 дней. С онлайн-оплатой и расчётом доставки — 19 990 ₽.
+Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -2510,12 +2499,12 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1s.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
         </is>
       </c>
     </row>
@@ -2621,9 +2610,7 @@
       <c r="W16" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Волгограде: без офиса и менеджеров, напрямую с разработчиком.
-Одностраничный сайт под одну услугу, который собирает заявки.
-Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
-С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -2641,12 +2628,12 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -2762,14 +2749,13 @@
           <t>В Краснодаре работаю удалённо — встречи не нужны, всё решаем в переписке.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -2788,12 +2774,12 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -2891,9 +2877,7 @@
       <c r="W18" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Саратове и по всей России, удалённо.
-Бот, который принимает заявки, пока вы заняты.
-Старт — 2 990 ₽, 1 день: бот-визитка с меню, ответами на частые вопросы и приёмом заявок вам в личку.
-Запись, оплата, выгрузка в таблицы — от 4 990 ₽, 1–2 дня.
+Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -2911,12 +2895,12 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1s.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
+          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
         </is>
       </c>
     </row>
@@ -3026,9 +3010,7 @@
       <c r="W19" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Тюмени онлайн: смета и срок — в первый день.
-Одностраничный сайт под одну услугу, который собирает заявки.
-Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
-С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -3046,12 +3028,12 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -3157,9 +3139,7 @@
       <c r="W20" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Тольятти: без офиса и менеджеров, напрямую с разработчиком.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит.
-Старт — 2 990 ₽, 1 день: одна страница на готовой структуре с вашими текстами и фото.
-Со своим дизайном и до 3 страниц — 4 990 ₽, 2–3 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -3179,12 +3159,12 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1s.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -3300,14 +3280,13 @@
           <t>В Ижевске работаю удалённо — встречи не нужны, всё решаем в переписке.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -3326,12 +3305,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3424,7 @@
       <c r="W22" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Барнауле и по всей России, удалённо.
-Многостраничный сайт компании: до 4 страниц — 9 990 ₽, до 6 страниц с онлайн-записью или калькулятором — 14 990 ₽. Срок 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -3455,7 +3434,7 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно те же работы стоят около 20 000 ₽, пакетом — от 9 990 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
 Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
@@ -3463,12 +3442,12 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1s.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3565,7 @@
       <c r="W23" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Ульяновске онлайн: смета и срок — в первый день.
-Магазин, в котором покупают, а не бросают корзину. До 50 товаров, заказы приходят вам в Telegram — 14 990 ₽, 7–10 дней. С онлайн-оплатой и расчётом доставки — 19 990 ₽.
+Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -3604,12 +3583,12 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1s.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
     </row>
@@ -3725,14 +3704,13 @@
           <t>Для бизнеса в Иркутске: без офиса и менеджеров, напрямую с разработчиком.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -3751,12 +3729,12 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -3862,9 +3840,7 @@
       <c r="W25" s="2" t="inlineStr">
         <is>
           <t>В Хабаровске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Одностраничный сайт под одну услугу, который собирает заявки.
-Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
-С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -3882,12 +3858,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
     </row>
@@ -4005,7 +3981,7 @@
       <c r="W26" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Ярославле и по всей России, удалённо.
-Сайт уже есть, но что-то не так — разберусь и починю. Мелкая правка — от 500 ₽, в тот же день.
+Сайт уже есть, но что-то не так — разберусь и починю. От 1 000 ₽, от 1 дня.
 С ЧЕМ ПРИХОДЯТ
 Нужны новые страницы или разделы
 Форма заявки не отправляется
@@ -4021,12 +3997,12 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/dorabotka-1s.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/dorabotka-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -4142,14 +4118,13 @@
           <t>Работаю с заказчиками во Владивостоке онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -4168,12 +4143,12 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -4279,9 +4254,7 @@
       <c r="W28" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Махачкале: без офиса и менеджеров, напрямую с разработчиком.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит.
-Старт — 2 990 ₽, 1 день: одна страница на готовой структуре с вашими текстами и фото.
-Со своим дизайном и до 3 страниц — 4 990 ₽, 2–3 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -4301,12 +4274,12 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1s.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -4404,9 +4377,7 @@
       <c r="W29" s="2" t="inlineStr">
         <is>
           <t>В Томске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Бот, который принимает заявки, пока вы заняты.
-Старт — 2 990 ₽, 1 день: бот-визитка с меню, ответами на частые вопросы и приёмом заявок вам в личку.
-Запись, оплата, выгрузка в таблицы — от 4 990 ₽, 1–2 дня.
+Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -4424,12 +4395,12 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1s.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg</t>
+          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -4545,14 +4516,13 @@
           <t>Делаю сайты и ботов для бизнеса в Оренбурге и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -4571,12 +4541,12 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -4682,9 +4652,7 @@
       <c r="W31" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Кемерово онлайн: смета и срок — в первый день.
-Одностраничный сайт под одну услугу, который собирает заявки.
-Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
-С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -4702,12 +4670,12 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -4813,9 +4781,7 @@
       <c r="W32" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Новокузнецке: без офиса и менеджеров, напрямую с разработчиком.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит.
-Старт — 2 990 ₽, 1 день: одна страница на готовой структуре с вашими текстами и фото.
-Со своим дизайном и до 3 страниц — 4 990 ₽, 2–3 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -4835,12 +4801,12 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1s.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4920,7 @@
       <c r="W33" s="2" t="inlineStr">
         <is>
           <t>В Рязани работаю удалённо — встречи не нужны, всё решаем в переписке.
-Многостраничный сайт компании: до 4 страниц — 9 990 ₽, до 6 страниц с онлайн-записью или калькулятором — 14 990 ₽. Срок 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -4964,7 +4930,7 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно те же работы стоят около 20 000 ₽, пакетом — от 9 990 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
 Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
@@ -4972,12 +4938,12 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1s.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -5093,14 +5059,13 @@
           <t>Делаю сайты и ботов для бизнеса в Набережных Челнах и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -5119,12 +5084,12 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -5230,9 +5195,7 @@
       <c r="W35" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Астрахани онлайн: смета и срок — в первый день.
-Одностраничный сайт под одну услугу, который собирает заявки.
-Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
-С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -5250,12 +5213,12 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5332,7 @@
       <c r="W36" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Пензе: без офиса и менеджеров, напрямую с разработчиком.
-Магазин, в котором покупают, а не бросают корзину. До 50 товаров, заказы приходят вам в Telegram — 14 990 ₽, 7–10 дней. С онлайн-оплатой и расчётом доставки — 19 990 ₽.
+Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -5387,12 +5350,12 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1s.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg</t>
         </is>
       </c>
     </row>
@@ -5508,14 +5471,13 @@
           <t>В Кирове работаю удалённо — встречи не нужны, всё решаем в переписке.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -5534,12 +5496,12 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -5641,9 +5603,7 @@
       <c r="W38" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Липецке и по всей России, удалённо.
-Бот, который принимает заявки, пока вы заняты.
-Старт — 2 990 ₽, 1 день: бот-визитка с меню, ответами на частые вопросы и приёмом заявок вам в личку.
-Запись, оплата, выгрузка в таблицы — от 4 990 ₽, 1–2 дня.
+Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, срок 1–2 дня.
 ЧТО УМЕЕТ
 Принимает заявки и складывает их в таблицу или CRM
 Записывает клиентов на время и напоминает о визите
@@ -5661,12 +5621,12 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1s.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg</t>
+          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -5772,9 +5732,7 @@
       <c r="W39" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Чебоксарах онлайн: смета и срок — в первый день.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит.
-Старт — 2 990 ₽, 1 день: одна страница на готовой структуре с вашими текстами и фото.
-Со своим дизайном и до 3 страниц — 4 990 ₽, 2–3 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -5794,12 +5752,12 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1s.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -5915,14 +5873,13 @@
           <t>Для бизнеса в Калининграде: без офиса и менеджеров, напрямую с разработчиком.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -5941,12 +5898,12 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -6052,9 +6009,7 @@
       <c r="W41" s="2" t="inlineStr">
         <is>
           <t>В Туле работаю удалённо — встречи не нужны, всё решаем в переписке.
-Одностраничный сайт под одну услугу, который собирает заявки.
-Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
-С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -6072,12 +6027,12 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6146,7 @@
       <c r="W42" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Курске и по всей России, удалённо.
-Сайт уже есть, но что-то не так — разберусь и починю. Мелкая правка — от 500 ₽, в тот же день.
+Сайт уже есть, но что-то не так — разберусь и починю. От 1 000 ₽, от 1 дня.
 С ЧЕМ ПРИХОДЯТ
 Нужны новые страницы или разделы
 Форма заявки не отправляется
@@ -6207,12 +6162,12 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/dorabotka-1s.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/dorabotka-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -6328,14 +6283,13 @@
           <t>Работаю с заказчиками в Сочи онлайн: смета и срок — в первый день.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -6354,12 +6308,12 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -6473,7 +6427,7 @@
       <c r="W44" s="2" t="inlineStr">
         <is>
           <t>Для бизнеса в Ставрополе: без офиса и менеджеров, напрямую с разработчиком.
-Многостраничный сайт компании: до 4 страниц — 9 990 ₽, до 6 страниц с онлайн-записью или калькулятором — 14 990 ₽. Срок 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
+Многостраничный сайт компании — от 14 990 ₽, 5–8 дней. Разделы, услуги, кейсы, команда, контакты. И админка, чтобы править всё самому.
 ЧТО ВХОДИТ
 До 6 страниц, каждая под свой поисковый запрос
 Свой дизайн, а не готовый шаблон
@@ -6483,7 +6437,7 @@
 Метрика с целями и SEO-разметка
 Домен, хостинг и SSL без доплаты
 30 дней правок после сдачи
-Поштучно те же работы стоят около 20 000 ₽, пакетом — от 9 990 ₽.
+Поштучно те же работы стоят около 20 000 ₽, пакетом — 14 990 ₽.
 Расскажите про компанию и услуги — назову точную цену и срок.
 Цены в объявлении — специальные для Авито. Почему дешевле рынка: работаю один, без офиса и менеджеров — вы не платите за агентство. По рынку такие работы стоят в 2–5 раз дороже. Работаю по договору.
 Работаю удалённо по всей России: всё обсуждаем в переписке или созвоне, ехать никуда не нужно. Портфолио из 35 работ покажу в переписке.</t>
@@ -6491,12 +6445,12 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1s.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -6602,9 +6556,7 @@
       <c r="W45" s="2" t="inlineStr">
         <is>
           <t>В Улан-Удэ работаю удалённо — встречи не нужны, всё решаем в переписке.
-Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит.
-Старт — 2 990 ₽, 1 день: одна страница на готовой структуре с вашими текстами и фото.
-Со своим дизайном и до 3 страниц — 4 990 ₽, 2–3 дня.
+Сайт-визитка, чтобы вас находили в поиске и сразу понимали, что вы делаете и сколько это стоит. От 4 990 ₽, 2–3 дня.
 ЧТО БУДЕТ НА САЙТЕ
 Услуги и цены
 Работы или фото
@@ -6624,12 +6576,12 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1s.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -6735,9 +6687,7 @@
       <c r="W46" s="2" t="inlineStr">
         <is>
           <t>Делаю сайты и ботов для бизнеса в Твери и по всей России, удалённо.
-Одностраничный сайт под одну услугу, который собирает заявки.
-Старт — 3 990 ₽, 1–2 дня: лендинг на проверенной структуре под вашу услугу.
-С дизайном под ваш бренд — 5 990 ₽, 2–4 дня.
+Одностраничный сайт под одну услугу, который собирает заявки. От 5 990 ₽, 2–4 дня.
 ЧТО ВХОДИТ
 Структура: что за чем идёт, чтобы человек дочитал и написал
 Дизайн под ваш продукт, без шаблонной «рыбы»
@@ -6755,12 +6705,12 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1s.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -6858,7 +6808,7 @@
       <c r="W47" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками в Магнитогорске онлайн: смета и срок — в первый день.
-Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 7 990 ₽.
+Подключаю нейросеть к Telegram или к вашему сайту, чтобы она отвечала клиентам вместо автоответчика с кнопками. От 9 990 ₽.
 В ЧЁМ РАЗНИЦА
 Обычный бот ведёт по кнопкам и теряет человека на первом вопросе не по сценарию. Бот с ИИ понимает вопрос словами и отвечает по вашим данным.
 ЧТО ДЕЛАЮ
@@ -6875,12 +6825,12 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-2s.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-ai.jpg</t>
+          <t>https://ysddev.com/avito/bot-2h.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-ai.jpg</t>
         </is>
       </c>
     </row>
@@ -6996,14 +6946,13 @@
           <t>Для бизнеса в Иванове: без офиса и менеджеров, напрямую с разработчиком.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -7022,12 +6971,12 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7090,7 @@
       <c r="W49" s="2" t="inlineStr">
         <is>
           <t>В Брянске работаю удалённо — встречи не нужны, всё решаем в переписке.
-Есть макет — сверстаю. От 1 990 ₽ за страницу, от 1 дня.
+Есть макет — сверстаю. От 2 490 ₽ за страницу, от 1 дня.
 КАК ВЕРСТАЮ
 Пиксель в пиксель по макету
 Адаптив: телефон, планшет, компьютер
@@ -7157,12 +7106,12 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/figma-1s.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/figma-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -7278,14 +7227,13 @@
           <t>Делаю сайты и ботов для бизнеса в Белгороде и по всей России, удалённо.
 Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
 ЦЕНЫ И СРОКИ
-Старт — 2 990 ₽, 1 день: одностраничный сайт на готовой структуре, ваши тексты и фото, форма заявки, адаптив
-Сайт-визитка со своим дизайном — 4 990 ₽, 2–3 дня
-Лендинг под рекламу — 5 990 ₽, 2–4 дня
-Многостраничный сайт — от 9 990 ₽, 5–8 дней
-Интернет-магазин — от 14 990 ₽, 7–14 дней
+Сайт-визитка — от 4 990 ₽, 2–3 дня
+Лендинг — от 5 990 ₽, 2–4 дня
+Многостраничный сайт — от 14 990 ₽, 5–8 дней
+Интернет-магазин — от 19 990 ₽, 10–14 дней
 Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ В ЛЮБОЙ ПАКЕТ
-Структура под вашу задачу
+ЧТО ВХОДИТ
+Структура и дизайн под вашу задачу, не шаблон
 Вёрстка под телефон и планшет
 Форма заявки с уведомлением вам в Telegram
 Базовое SEO: заголовки, описания, карта сайта, скорость
@@ -7304,12 +7252,12 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1s.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7371,7 @@
       <c r="W51" s="2" t="inlineStr">
         <is>
           <t>Работаю с заказчиками во Владимире онлайн: смета и срок — в первый день.
-Магазин, в котором покупают, а не бросают корзину. До 50 товаров, заказы приходят вам в Telegram — 14 990 ₽, 7–10 дней. С онлайн-оплатой и расчётом доставки — 19 990 ₽.
+Магазин, в котором покупают, а не бросают корзину. От 19 990 ₽, 10–14 дней. С онлайн-оплатой и расчётом доставки — пакет 24 990 ₽.
 ЧТО ВХОДИТ
 Каталог с фильтрами и поиском
 Карточки товаров: фото, описания, характеристики
@@ -7441,12 +7389,12 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1s.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg</t>
+          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
+          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-2h.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
+          <t>https://ysddev.com/avito/bot-2h.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/figma-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/figma-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg</t>
+          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/dorabotka-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/dorabotka-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg</t>
+          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/sayt-3.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg</t>
+          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/dorabotka-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/dorabotka-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-2h.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-ai.jpg</t>
+          <t>https://ysddev.com/avito/bot-2h.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/figma-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/figma-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/lending-1o.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1o.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1o.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
+          <t>https://ysddev.com/avito/bot-1o.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-info-1o.jpg | https://ysddev.com/avito/bot-info-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/lending-1o.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1o.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-2h.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
+          <t>https://ysddev.com/avito/bot-2o.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-info-1o.jpg | https://ysddev.com/avito/bot-info-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/figma-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/figma-1o.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1o.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/lending-1o.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
+          <t>https://ysddev.com/avito/bot-1o.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-info-1o.jpg | https://ysddev.com/avito/bot-info-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/lending-1o.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1o.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1o.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1o.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/lending-1o.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/dorabotka-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/dorabotka-1o.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1o.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
+          <t>https://ysddev.com/avito/bot-1o.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-info-1o.jpg | https://ysddev.com/avito/bot-info-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/lending-1o.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1o.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1o.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/lending-1o.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1o.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-1h.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
+          <t>https://ysddev.com/avito/bot-1o.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-info-1o.jpg | https://ysddev.com/avito/bot-info-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1o.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/lending-1o.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/dorabotka-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/dorabotka-1o.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/korp-1h.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/korp-1o.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/prez-it.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-1o.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/korp-yurist.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-1h.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-2.jpg</t>
+          <t>https://ysddev.com/avito/lending-1o.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-2h.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-info-1.jpg | https://ysddev.com/avito/bot-info-2.jpg</t>
+          <t>https://ysddev.com/avito/bot-2o.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/bot-salon.jpg | https://ysddev.com/avito/bot-restoran.jpg | https://ysddev.com/avito/bot-ai.jpg | https://ysddev.com/avito/bot-info-1o.jpg | https://ysddev.com/avito/bot-info-2o.jpg</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/figma-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/figma-1o.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-salon.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-1h.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
+          <t>https://ysddev.com/avito/sayt-1o.jpg | https://ysddev.com/avito/sayt-fitnes.jpg | https://ysddev.com/avito/sayt-stomatologiya.jpg | https://ysddev.com/avito/sayt-stroitelstvo.jpg | https://ysddev.com/avito/sayt-remont.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/korp-logistika.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/sayt-restoran.jpg | https://ysddev.com/avito/sayt-turagentstvo.jpg</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/magazin-1h.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-2.jpg | https://ysddev.com/avito/sayt-3.jpg</t>
+          <t>https://ysddev.com/avito/magazin-1o.jpg | https://ysddev.com/avito/bot-dostavka.jpg | https://ysddev.com/avito/magazin-mebel.jpg | https://ysddev.com/avito/bot-podderzhka.jpg | https://ysddev.com/avito/prez-magazin.jpg | https://ysddev.com/avito/sayt-nedvizhimost.jpg | https://ysddev.com/avito/sayt-2o.jpg | https://ysddev.com/avito/sayt-3o.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -709,7 +709,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -722,7 +722,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -856,7 +856,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-33.jpg | https://ysddev.com/avito/p-16.jpg | https://ysddev.com/avito/p-15.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-13.jpg | https://ysddev.com/avito/p-34.jpg | https://ysddev.com/avito/p-12.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-12.jpg | https://ysddev.com/avito/p-14.jpg | https://ysddev.com/avito/p-11.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-32.jpg | https://ysddev.com/avito/p-35.jpg | https://ysddev.com/avito/p-38.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-38.jpg | https://ysddev.com/avito/p-39.jpg | https://ysddev.com/avito/p-33.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-16.jpg | https://ysddev.com/avito/p-15.jpg | https://ysddev.com/avito/p-13.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-13.jpg | https://ysddev.com/avito/p-34.jpg | https://ysddev.com/avito/p-12.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-14.jpg | https://ysddev.com/avito/p-11.jpg | https://ysddev.com/avito/p-32.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-32.jpg | https://ysddev.com/avito/p-35.jpg | https://ysddev.com/avito/p-38.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-39.jpg | https://ysddev.com/avito/p-33.jpg | https://ysddev.com/avito/p-16.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-16.jpg | https://ysddev.com/avito/p-15.jpg | https://ysddev.com/avito/p-13.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-34.jpg | https://ysddev.com/avito/p-12.jpg | https://ysddev.com/avito/p-14.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-14.jpg | https://ysddev.com/avito/p-11.jpg | https://ysddev.com/avito/p-32.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-35.jpg | https://ysddev.com/avito/p-38.jpg | https://ysddev.com/avito/p-39.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-39.jpg | https://ysddev.com/avito/p-33.jpg | https://ysddev.com/avito/p-16.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-15.jpg | https://ysddev.com/avito/p-13.jpg | https://ysddev.com/avito/p-34.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3972,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4119,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-34.jpg | https://ysddev.com/avito/p-12.jpg | https://ysddev.com/avito/p-14.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-11.jpg | https://ysddev.com/avito/p-32.jpg | https://ysddev.com/avito/p-35.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-35.jpg | https://ysddev.com/avito/p-38.jpg | https://ysddev.com/avito/p-39.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-33.jpg | https://ysddev.com/avito/p-16.jpg | https://ysddev.com/avito/p-15.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-15.jpg | https://ysddev.com/avito/p-13.jpg | https://ysddev.com/avito/p-34.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-12.jpg | https://ysddev.com/avito/p-14.jpg | https://ysddev.com/avito/p-11.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5213,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-11.jpg | https://ysddev.com/avito/p-32.jpg | https://ysddev.com/avito/p-35.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-38.jpg | https://ysddev.com/avito/p-39.jpg | https://ysddev.com/avito/p-33.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-33.jpg | https://ysddev.com/avito/p-16.jpg | https://ysddev.com/avito/p-15.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-13.jpg | https://ysddev.com/avito/p-34.jpg | https://ysddev.com/avito/p-12.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-12.jpg | https://ysddev.com/avito/p-14.jpg | https://ysddev.com/avito/p-11.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-32.jpg | https://ysddev.com/avito/p-35.jpg | https://ysddev.com/avito/p-38.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -6437,7 +6437,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-38.jpg | https://ysddev.com/avito/p-39.jpg | https://ysddev.com/avito/p-33.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-16.jpg | https://ysddev.com/avito/p-15.jpg | https://ysddev.com/avito/p-13.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -6832,7 +6832,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-13.jpg | https://ysddev.com/avito/p-34.jpg | https://ysddev.com/avito/p-12.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-14.jpg | https://ysddev.com/avito/p-11.jpg | https://ysddev.com/avito/p-32.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-32.jpg | https://ysddev.com/avito/p-35.jpg | https://ysddev.com/avito/p-38.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-39.jpg | https://ysddev.com/avito/p-33.jpg | https://ysddev.com/avito/p-16.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7652,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8231,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-16.jpg | https://ysddev.com/avito/p-15.jpg | https://ysddev.com/avito/p-13.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-34.jpg | https://ysddev.com/avito/p-12.jpg | https://ysddev.com/avito/p-14.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8937,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-14.jpg | https://ysddev.com/avito/p-11.jpg | https://ysddev.com/avito/p-32.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-35.jpg | https://ysddev.com/avito/p-38.jpg | https://ysddev.com/avito/p-39.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10339,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -10473,7 +10473,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -10767,7 +10767,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -11061,7 +11061,7 @@
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -11182,7 +11182,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11309,7 @@
 ПОЧЕМУ БОТ
 Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
 Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, что бот должен делать — покажу похожие примеры.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/p-39.jpg | https://ysddev.com/avito/p-33.jpg | https://ysddev.com/avito/p-16.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/p-15.jpg | https://ysddev.com/avito/p-13.jpg | https://ysddev.com/avito/p-34.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
         </is>
       </c>
     </row>
@@ -11456,7 +11456,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11750,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -11897,7 +11897,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -12044,7 +12044,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12191,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -12325,7 +12325,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -12472,7 +12472,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -12485,7 +12485,7 @@
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -12619,7 +12619,7 @@
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12753,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12900,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -12913,7 +12913,7 @@
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13047,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -13181,7 +13181,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -13328,7 +13328,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13462,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-36.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -13903,7 +13903,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-37.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -14037,7 +14037,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/p-18.jpg | https://ysddev.com/avito/p-24.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-25.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -14184,7 +14184,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -14197,7 +14197,7 @@
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-28.jpg | https://ysddev.com/avito/p-22.jpg | https://ysddev.com/avito/p-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-17.jpg | https://ysddev.com/avito/p-30.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -14318,7 +14318,7 @@
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/p-19.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>
@@ -14465,7 +14465,7 @@
 Цена из сметы не растёт
 14 дней правок после сдачи бесплатно (на магазин — 60)
 Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 53 работы — часть на фото, остальные пришлю в переписке.
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
 Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/p-21.jpg | https://ysddev.com/avito/p-26.jpg | https://ysddev.com/avito/p-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/p-23.jpg | https://ysddev.com/avito/p-27.jpg | https://ysddev.com/avito/p-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/q-16.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-15.jpg | https://ysddev.com/avito/q-13.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-34.jpg | https://ysddev.com/avito/q-12.jpg | https://ysddev.com/avito/q-14.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-11.jpg | https://ysddev.com/avito/q-32.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11061,7 @@
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-f.jpg | https://ysddev.com/avito/q-35.jpg | https://ysddev.com/avito/q-38.jpg | https://ysddev.com/avito/q-39.jpg | https://ysddev.com/avito/bot-4f.jpg | https://ysddev.com/avito/q-56.jpg | https://ysddev.com/avito/q-57.jpg | https://ysddev.com/avito/q-33.jpg | https://ysddev.com/avito/bot-info-1f.jpg | https://ysddev.com/avito/bot-info-2f.jpg</t>
+          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12485,7 +12485,7 @@
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12619,7 +12619,7 @@
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12913,7 +12913,7 @@
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-17.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-23.jpg | https://ysddev.com/avito/q-27.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-f.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-29.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14197,7 +14197,7 @@
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/q-36.jpg | https://ysddev.com/avito/q-37.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-54.jpg | https://ysddev.com/avito/q-55.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-f.jpg | https://ysddev.com/avito/q-30.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-31.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-21.jpg | https://ysddev.com/avito/q-26.jpg | https://ysddev.com/avito/q-20.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-f.jpg | https://ysddev.com/avito/q-24.jpg | https://ysddev.com/avito/q-25.jpg | https://ysddev.com/avito/q-18.jpg | https://ysddev.com/avito/sayt-4f.jpg | https://ysddev.com/avito/q-19.jpg | https://ysddev.com/avito/q-28.jpg | https://ysddev.com/avito/q-22.jpg | https://ysddev.com/avito/sayt-2f.jpg | https://ysddev.com/avito/sayt-3f.jpg</t>
+          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11061,7 @@
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12485,7 +12485,7 @@
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12619,7 +12619,7 @@
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12913,7 +12913,7 @@
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14197,7 +14197,7 @@
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-moskva-sayt.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-moskva-lending-2.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-moskva-bot-2.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-sankt-peterburg-lending.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-sankt-peterburg-sayt-2.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-sankt-peterburg-bot-2.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-novosibirsk-magazin.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-novosibirsk-lending-2.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-novosibirsk-bot-2.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-004.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-ekaterinburg-vizitka-2.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-ekaterinburg-bot-2.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/8253207537.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-kazan-lending-2.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-kazan-bot-2.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-nizhniy-novgorod-sayt.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-nizhniy-novgorod-vizitka-2.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-nizhniy-novgorod-bot-2.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-012.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-krasnoyarsk-lending-2.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-krasnoyarsk-bot-2.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-chelyabinsk-bot.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-chelyabinsk-sayt-2.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-chelyabinsk-vizitka-2.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-samara-lending.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-samara-sayt-2.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-samara-bot-2.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-011.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-ufa-sayt-2.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-ufa-vizitka-2.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-rostov-na-donu-korp.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-rostov-na-donu-lending-2.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-rostov-na-donu-bot-2.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-krasnodar-sayt.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-krasnodar-vizitka-2.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-krasnodar-bot-2.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-omsk-sayt.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-omsk-lending-2.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-omsk-bot-2.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-voronezh-sayt.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-voronezh-vizitka-2.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-voronezh-bot-2.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-perm-magazin.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-perm-lending-2.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-perm-bot-2.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-volgograd-lending.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-volgograd-sayt-2.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-volgograd-bot-2.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-saratov-bot.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-018.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-tolyatti-vizitka.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-izhevsk-sayt.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-barnaul-korp.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-022.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-irkutsk-sayt.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-habarovsk-lending.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-024.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-vladivostok-sayt.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-mahachkala-vizitka.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/w-16-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-15-h.jpg | https://ysddev.com/avito/w-13-h.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-tomsk-bot.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-orenburg-sayt.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-kemerovo-lending.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-novokuzneck-vizitka.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-ryazan-korp.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-naberezhnye-chelny-sayt.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-astrahan-lending.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-penza-magazin.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-kirov-sayt.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-34-h.jpg | https://ysddev.com/avito/w-12-h.jpg | https://ysddev.com/avito/w-14-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-11-h.jpg | https://ysddev.com/avito/w-32-h.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-030.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-cheboksary-vizitka.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-kaliningrad-sayt.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-tula-lending.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-kursk-dorabotka.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-sochi-sayt.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-stavropol-korp.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11061,7 @@
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-ulan-ude-vizitka.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-tver-lending.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/bot-r.jpg | https://ysddev.com/avito/w-35-h.jpg | https://ysddev.com/avito/w-38-h.jpg | https://ysddev.com/avito/w-39-h.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w-56-h.jpg | https://ysddev.com/avito/w-57-h.jpg | https://ysddev.com/avito/w-33-h.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-magnitogorsk-ai.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-ivanovo-sayt.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-bryansk-figma.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-belgorod-sayt.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-vladimir-magazin.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-surgut-sayt.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-arhangelsk-sayt.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-chita-lending.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12485,7 +12485,7 @@
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-kaluga-sayt.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12619,7 +12619,7 @@
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-smolensk-vizitka.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-yakutsk-sayt.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12913,7 +12913,7 @@
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-saransk-sayt.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-vologda-sayt.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-kurgan-lending.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-orel-sayt.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-vladikavkaz-vizitka.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-murmansk-sayt.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-17-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-tambov-sayt.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-23-h.jpg | https://ysddev.com/avito/w-27-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-petrozavodsk-sayt.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/lending-r.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-29-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-kostroma-lending.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14197,7 +14197,7 @@
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/w-36-h.jpg | https://ysddev.com/avito/w-37-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-54-h.jpg | https://ysddev.com/avito/w-55-h.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-yoshkar-ola-sayt.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/vizitka-r.jpg | https://ysddev.com/avito/w-30-h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-31-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-21-h.jpg | https://ysddev.com/avito/w-26-h.jpg | https://ysddev.com/avito/w-20-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-syktyvkar-vizitka.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/sayt-r.jpg | https://ysddev.com/avito/w-24-h.jpg | https://ysddev.com/avito/w-25-h.jpg | https://ysddev.com/avito/w-18-h.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w-19-h.jpg | https://ysddev.com/avito/w-28-h.jpg | https://ysddev.com/avito/w-22-h.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-novorossiysk-sayt.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -856,7 +856,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-moskva-lending-2.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-moskva-lending-2-b.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-ekaterinburg-bot-2.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-ekaterinburg-bot-2-b.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/8253207537.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/8253207537-b.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-nizhniy-novgorod-vizitka-2.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-nizhniy-novgorod-vizitka-2-b.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-samara-lending.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-samara-lending-b.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-rostov-na-donu-bot-2.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-rostov-na-donu-bot-2-b.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-krasnodar-vizitka-2.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-krasnodar-vizitka-2-b.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-saratov-bot.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-saratov-bot-b.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-018.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-018-b.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-izhevsk-sayt.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-izhevsk-sayt-b.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-mahachkala-vizitka.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-mahachkala-vizitka-b.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11061,7 @@
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-ulan-ude-vizitka.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-ulan-ude-vizitka-b.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-tver-lending.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-tver-lending-b.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-belgorod-sayt.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-belgorod-sayt-b.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-tambov-sayt.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-tambov-sayt-b.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-syktyvkar-vizitka.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c/ysd-syktyvkar-vizitka-b.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -683,34 +683,36 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Создание сайтов под ключ</t>
+          <t>Создание сайтов под ключ. Макет бесплатно</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Делаю сайты для бизнеса в Москве и по всей России — удалённо, напрямую, без менеджеров.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Делаю сайты для бизнеса в Москве и по всей России — удалённо, напрямую, без менеджеров.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -722,7 +724,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-moskva-sayt.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-moskva-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -822,29 +824,34 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Лендинг под ключ за 1–2 дня</t>
+          <t>Лендинг под ключ за 1–2 дня. Макет бесплатно</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>Делаю лендинги и сайты-визитки для бизнеса в Москве — удалённо, за 1–2 дня.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Делаю лендинги и сайты-визитки для бизнеса в Москве — удалённо, за 1–2 дня.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -856,7 +863,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-moskva-lending-2-b.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-moskva-lending-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -948,30 +955,37 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Telegram-бот для бизнеса</t>
+          <t>Telegram-бот под ключ за 1 день</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>Делаю Telegram-ботов для бизнеса в Москве и по всей России — удалённо.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Делаю Telegram-ботов для бизнеса в Москве и по всей России — удалённо.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -983,7 +997,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-moskva-bot-2.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-moskva-bot-2.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1083,29 +1097,34 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Создание лендинга под ключ</t>
+          <t>Продающий лендинг под рекламу за 2 дня</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>Одностраничный сайт под рекламу и соцсети — для бизнеса в Санкт-Петербурге и по всей России.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Одностраничный сайт под рекламу и соцсети — для бизнеса в Санкт-Петербурге и по всей России.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -1117,7 +1136,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-sankt-peterburg-lending.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-sankt-peterburg-lending.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1225,34 +1244,36 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Сайт под ключ — макет до оплаты</t>
+          <t>Сайт для бизнеса за 1–2 дня под ключ</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>Работаю с заказчиками в Санкт-Петербурге онлайн: смета и срок — в первый день.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Работаю с заказчиками в Санкт-Петербурге онлайн: смета и срок — в первый день.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -1264,7 +1285,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-sankt-peterburg-sayt-2.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-sankt-peterburg-sayt-2.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1356,30 +1377,37 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Разработка Telegram-бота под ключ</t>
+          <t>Telegram-бот для записи и заявок</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>Бот для заявок, записи и оплаты — для бизнеса в Санкт-Петербурге. Простой бот запускаю за 1 день.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Бот для заявок, записи и оплаты — для бизнеса в Санкт-Петербурге. Простой бот запускаю за 1 день.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -1391,7 +1419,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-sankt-peterburg-bot-2.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-sankt-peterburg-bot-2.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1499,34 +1527,36 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Сайт под ключ: визитка, лендинг, магазин</t>
+          <t>Интернет-магазин под ключ за 5–7 дней</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>Для бизнеса в Новосибирске: делаю сайт сам, без офиса и наценки агентства.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Для бизнеса в Новосибирске: делаю сайт сам, без офиса и наценки агентства.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -1538,7 +1568,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-novosibirsk-magazin.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-novosibirsk-magazin.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1638,29 +1668,34 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Продающий лендинг под ключ</t>
+          <t>Лендинг, который собирает заявки</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>В Новосибирске работаю удалённо: бриф, макет, запуск — без встреч и поездок.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+В Новосибирске работаю удалённо: бриф, макет, запуск — без встреч и поездок.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -1672,7 +1707,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-novosibirsk-lending-2.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-novosibirsk-lending-2.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1764,30 +1799,37 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Telegram-бот для записи и заявок</t>
+          <t>Бот в Telegram: запись, оплата, рассылки</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>В Новосибирске работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+В Новосибирске работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -1799,7 +1841,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-novosibirsk-bot-2.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-novosibirsk-bot-2.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1911,34 +1953,36 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Сайт для компании под ключ</t>
+          <t>Сайт компании под ключ за 3–5 дней</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>В Екатеринбурге работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+В Екатеринбурге работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -1950,7 +1994,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-004.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-004.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2050,29 +2094,34 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка под ключ</t>
+          <t>Сайт-визитка за 1–2 дня. Макет бесплатно</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>Для мастеров и компаний в Екатеринбурге: быстрый сайт, с которого приходят заявки.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Для мастеров и компаний в Екатеринбурге: быстрый сайт, с которого приходят заявки.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -2084,7 +2133,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-ekaterinburg-vizitka-2.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-ekaterinburg-vizitka-2.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2176,30 +2225,37 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Создание Telegram-бота за 1 день</t>
+          <t>Чат-бот в Telegram для бизнеса</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>Делаю Telegram-ботов для бизнеса в Екатеринбурге и по всей России — удалённо.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Делаю Telegram-ботов для бизнеса в Екатеринбурге и по всей России — удалённо.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -2211,7 +2267,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-ekaterinburg-bot-2-b.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-ekaterinburg-bot-2.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2323,34 +2379,36 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Разработка сайта под ключ за 1–2 дня</t>
+          <t>Разработка сайтов: сначала макет, потом оплата</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>Сайты для компаний и частных мастеров в Казани — от макета до запуска на вашем домене.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Сайты для компаний и частных мастеров в Казани — от макета до запуска на вашем домене.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -2362,7 +2420,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/8253207537-b.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/8253207537.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2462,29 +2520,34 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Лендинг для рекламы и соцсетей</t>
+          <t>Лендинг для рекламы и соцсетей под ключ</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>Делаю лендинги и сайты-визитки для бизнеса в Казани — удалённо, за 1–2 дня.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Делаю лендинги и сайты-визитки для бизнеса в Казани — удалённо, за 1–2 дня.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -2496,7 +2559,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-kazan-lending-2.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-kazan-lending-2.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2588,30 +2651,37 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Бот для записи клиентов в Telegram</t>
+          <t>Telegram-бот для заказов и оплаты</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>Бот для заявок, записи и оплаты — для бизнеса в Казани. Простой бот запускаю за 1 день.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Бот для заявок, записи и оплаты — для бизнеса в Казани. Простой бот запускаю за 1 день.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -2623,7 +2693,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-kazan-bot-2.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-kazan-bot-2.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2731,34 +2801,36 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Создание сайта для бизнеса под ключ</t>
+          <t>Сайт, который приносит заявки, под ключ</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>Делаю сайты для бизнеса в Нижнем Новгороде и по всей России — удалённо, напрямую, без менеджеров.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Делаю сайты для бизнеса в Нижнем Новгороде и по всей России — удалённо, напрямую, без менеджеров.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -2770,7 +2842,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-nizhniy-novgorod-sayt.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-nizhniy-novgorod-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2870,29 +2942,34 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка для бизнеса за 1–2 дня</t>
+          <t>Сайт-визитка для бизнеса под ключ</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>Одностраничный сайт под рекламу и соцсети — для бизнеса в Нижнем Новгороде и по всей России.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Одностраничный сайт под рекламу и соцсети — для бизнеса в Нижнем Новгороде и по всей России.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -2904,7 +2981,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-nizhniy-novgorod-vizitka-2-b.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-nizhniy-novgorod-vizitka-2.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2996,30 +3073,37 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Telegram-бот для заказов и оплаты</t>
+          <t>Бот для записи клиентов в Telegram</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>В Нижнем Новгороде работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+В Нижнем Новгороде работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -3031,7 +3115,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-nizhniy-novgorod-bot-2.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-nizhniy-novgorod-bot-2.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3143,34 +3227,36 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Вёрстка и создание сайтов под ключ</t>
+          <t>Вёрстка из Figma и сайты под ключ</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>Работаю с заказчиками в Красноярске онлайн: смета и срок — в первый день.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Работаю с заказчиками в Красноярске онлайн: смета и срок — в первый день.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -3182,7 +3268,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-012.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-012.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3282,29 +3368,34 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Одностраничный сайт под ключ</t>
+          <t>Одностраничный сайт за 1–2 дня под ключ</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>В Красноярске работаю удалённо: бриф, макет, запуск — без встреч и поездок.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+В Красноярске работаю удалённо: бриф, макет, запуск — без встреч и поездок.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -3316,7 +3407,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-krasnoyarsk-lending-2.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-krasnoyarsk-lending-2.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3408,30 +3499,37 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Telegram-бот для бизнеса</t>
+          <t>Telegram-бот под ключ за 1 день</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>Делаю Telegram-ботов для бизнеса в Красноярске и по всей России — удалённо.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Делаю Telegram-ботов для бизнеса в Красноярске и по всей России — удалённо.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -3443,7 +3541,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-krasnoyarsk-bot-2.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-krasnoyarsk-bot-2.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3535,30 +3633,37 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Разработка Telegram-бота под ключ</t>
+          <t>Telegram-бот для записи и заявок</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>Бот для заявок, записи и оплаты — для бизнеса в Челябинске. Простой бот запускаю за 1 день.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Бот для заявок, записи и оплаты — для бизнеса в Челябинске. Простой бот запускаю за 1 день.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -3570,7 +3675,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-chelyabinsk-bot.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-chelyabinsk-bot.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3678,34 +3783,36 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Создание сайта с нуля под ключ</t>
+          <t>Создание сайта с нуля за 1–2 дня</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>Для бизнеса в Челябинске: делаю сайт сам, без офиса и наценки агентства.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Для бизнеса в Челябинске: делаю сайт сам, без офиса и наценки агентства.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -3717,7 +3824,7 @@
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-chelyabinsk-sayt-2.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-chelyabinsk-sayt-2.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3817,29 +3924,34 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка и лендинг под ключ</t>
+          <t>Сайт-визитка и лендинг за 1–2 дня</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>Для мастеров и компаний в Челябинске: быстрый сайт, с которого приходят заявки.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Для мастеров и компаний в Челябинске: быстрый сайт, с которого приходят заявки.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -3851,7 +3963,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-chelyabinsk-vizitka-2.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-chelyabinsk-vizitka-2.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3951,29 +4063,34 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Лендинг под ключ за 1–2 дня</t>
+          <t>Лендинг под ключ за 1–2 дня. Макет бесплатно</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>Делаю лендинги и сайты-визитки для бизнеса в Самаре — удалённо, за 1–2 дня.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Делаю лендинги и сайты-визитки для бизнеса в Самаре — удалённо, за 1–2 дня.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -3985,7 +4102,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-samara-lending-b.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-samara-lending.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4098,29 +4215,31 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>В Самаре работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+В Самаре работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -4132,7 +4251,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-samara-sayt-2.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-samara-sayt-2.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4224,30 +4343,37 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Telegram-бот для записи и заявок</t>
+          <t>Бот в Telegram: запись, оплата, рассылки</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>В Самаре работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+В Самаре работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -4259,7 +4385,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-samara-bot-2.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-samara-bot-2.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4355,30 +4481,37 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Чат-бот для бизнеса в Telegram</t>
+          <t>Чат-бот с ИИ для бизнеса в Telegram</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>Делаю Telegram-ботов для бизнеса в Уфе и по всей России — удалённо.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Делаю Telegram-ботов для бизнеса в Уфе и по всей России — удалённо.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -4390,7 +4523,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-011.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-011.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4498,34 +4631,36 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Разработка сайтов для бизнеса</t>
+          <t>Разработка сайтов для бизнеса. Макет бесплатно</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>Сайты для компаний и частных мастеров в Уфе — от макета до запуска на вашем домене.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Сайты для компаний и частных мастеров в Уфе — от макета до запуска на вашем домене.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -4537,7 +4672,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-ufa-sayt-2.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-ufa-sayt-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4637,29 +4772,34 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка под ключ</t>
+          <t>Сайт-визитка за 1–2 дня. Макет бесплатно</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>Одностраничный сайт под рекламу и соцсети — для бизнеса в Уфе и по всей России.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Одностраничный сайт под рекламу и соцсети — для бизнеса в Уфе и по всей России.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -4671,7 +4811,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-ufa-vizitka-2.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-ufa-vizitka-2.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4779,34 +4919,36 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Корпоративный сайт и сайт под ключ</t>
+          <t>Корпоративный сайт под ключ. Макет бесплатно</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>Делаю сайты для бизнеса в Ростове-на-Дону и по всей России — удалённо, напрямую, без менеджеров.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Делаю сайты для бизнеса в Ростове-на-Дону и по всей России — удалённо, напрямую, без менеджеров.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -4818,7 +4960,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-rostov-na-donu-korp.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-rostov-na-donu-korp.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4918,29 +5060,34 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Создание лендинга под ключ</t>
+          <t>Продающий лендинг под рекламу за 2 дня</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>В Ростове-на-Дону работаю удалённо: бриф, макет, запуск — без встреч и поездок.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+В Ростове-на-Дону работаю удалённо: бриф, макет, запуск — без встреч и поездок.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -4952,7 +5099,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-rostov-na-donu-lending-2.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-rostov-na-donu-lending-2.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5044,30 +5191,37 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Создание Telegram-бота за 1 день</t>
+          <t>Чат-бот в Telegram для бизнеса</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>Бот для заявок, записи и оплаты — для бизнеса в Ростове-на-Дону. Простой бот запускаю за 1 день.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Бот для заявок, записи и оплаты — для бизнеса в Ростове-на-Дону. Простой бот запускаю за 1 день.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -5079,7 +5233,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-rostov-na-donu-bot-2-b.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-rostov-na-donu-bot-2.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5187,34 +5341,36 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Сайт под ключ с формой заявок в Telegram</t>
+          <t>Сайт под ключ с заявками в Telegram</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>Работаю с заказчиками в Краснодаре онлайн: смета и срок — в первый день.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Работаю с заказчиками в Краснодаре онлайн: смета и срок — в первый день.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -5226,7 +5382,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-krasnodar-sayt.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-krasnodar-sayt.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5326,29 +5482,34 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка для бизнеса за 1–2 дня</t>
+          <t>Сайт-визитка для бизнеса под ключ</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>Для мастеров и компаний в Краснодаре: быстрый сайт, с которого приходят заявки.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Для мастеров и компаний в Краснодаре: быстрый сайт, с которого приходят заявки.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -5360,7 +5521,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-krasnodar-vizitka-2-b.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-krasnodar-vizitka-2.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5452,30 +5613,37 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Бот для записи клиентов в Telegram</t>
+          <t>Telegram-бот для заказов и оплаты</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>В Краснодаре работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+В Краснодаре работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -5487,7 +5655,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-krasnodar-bot-2.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-krasnodar-bot-2.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5595,34 +5763,36 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Веб-разработчик: сайт под ключ</t>
+          <t>Веб-разработчик: сайт за 1–2 дня под ключ</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>Для бизнеса в Омске: делаю сайт сам, без офиса и наценки агентства.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Для бизнеса в Омске: делаю сайт сам, без офиса и наценки агентства.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -5634,7 +5804,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-omsk-sayt.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-omsk-sayt.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5734,29 +5904,34 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Продающий лендинг под ключ</t>
+          <t>Лендинг, который собирает заявки</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>Делаю лендинги и сайты-визитки для бизнеса в Омске — удалённо, за 1–2 дня.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Делаю лендинги и сайты-визитки для бизнеса в Омске — удалённо, за 1–2 дня.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -5768,7 +5943,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-omsk-lending-2.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-omsk-lending-2.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5860,30 +6035,37 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Telegram-бот для заказов и оплаты</t>
+          <t>Бот для записи клиентов в Telegram</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>Делаю Telegram-ботов для бизнеса в Омске и по всей России — удалённо.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Делаю Telegram-ботов для бизнеса в Омске и по всей России — удалённо.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -5895,7 +6077,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-omsk-bot-2.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-omsk-bot-2.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6003,34 +6185,36 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Создание сайтов под ключ</t>
+          <t>Создание сайтов под ключ. Макет бесплатно</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>В Воронеже работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+В Воронеже работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -6042,7 +6226,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-voronezh-sayt.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-voronezh-sayt.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6142,29 +6326,34 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка и лендинг под ключ</t>
+          <t>Сайт-визитка и лендинг за 1–2 дня</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>Одностраничный сайт под рекламу и соцсети — для бизнеса в Воронеже и по всей России.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Одностраничный сайт под рекламу и соцсети — для бизнеса в Воронеже и по всей России.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -6176,7 +6365,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-voronezh-vizitka-2.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-voronezh-vizitka-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6268,30 +6457,37 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Telegram-бот для бизнеса</t>
+          <t>Telegram-бот под ключ за 1 день</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>Бот для заявок, записи и оплаты — для бизнеса в Воронеже. Простой бот запускаю за 1 день.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Бот для заявок, записи и оплаты — для бизнеса в Воронеже. Простой бот запускаю за 1 день.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -6303,7 +6499,7 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-voronezh-bot-2.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-voronezh-bot-2.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6411,34 +6607,36 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Интернет-магазин и сайт под ключ</t>
+          <t>Сайт и интернет-магазин под ключ</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>Сайты для компаний и частных мастеров в Перми — от макета до запуска на вашем домене.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Сайты для компаний и частных мастеров в Перми — от макета до запуска на вашем домене.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -6450,7 +6648,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-perm-magazin.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-perm-magazin.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6550,29 +6748,34 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Лендинг для рекламы и соцсетей</t>
+          <t>Лендинг для рекламы и соцсетей под ключ</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>В Перми работаю удалённо: бриф, макет, запуск — без встреч и поездок.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+В Перми работаю удалённо: бриф, макет, запуск — без встреч и поездок.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -6584,7 +6787,7 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-perm-lending-2.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-perm-lending-2.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6676,30 +6879,37 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Разработка Telegram-бота под ключ</t>
+          <t>Telegram-бот для записи и заявок</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>В Перми работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+В Перми работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -6711,7 +6921,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-perm-bot-2.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-perm-bot-2.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6811,29 +7021,34 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Одностраничный сайт под ключ</t>
+          <t>Одностраничный сайт за 1–2 дня под ключ</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>Для мастеров и компаний в Волгограде: быстрый сайт, с которого приходят заявки.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Для мастеров и компаний в Волгограде: быстрый сайт, с которого приходят заявки.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -6845,7 +7060,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-volgograd-lending.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-volgograd-lending.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6953,34 +7168,36 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Сайт под ключ — макет до оплаты</t>
+          <t>Сайт для бизнеса за 1–2 дня под ключ</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>Делаю сайты для бизнеса в Волгограде и по всей России — удалённо, напрямую, без менеджеров.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Делаю сайты для бизнеса в Волгограде и по всей России — удалённо, напрямую, без менеджеров.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -6992,7 +7209,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-volgograd-sayt-2.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-volgograd-sayt-2.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7084,30 +7301,37 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Telegram-бот для записи и заявок</t>
+          <t>Бот в Telegram: запись, оплата, рассылки</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>Делаю Telegram-ботов для бизнеса в Волгограде и по всей России — удалённо.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Делаю Telegram-ботов для бизнеса в Волгограде и по всей России — удалённо.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -7119,7 +7343,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-volgograd-bot-2.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-volgograd-bot-2.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7211,30 +7435,37 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Создание Telegram-бота за 1 день</t>
+          <t>Чат-бот в Telegram для бизнеса</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>Бот для заявок, записи и оплаты — для бизнеса в Саратове. Простой бот запускаю за 1 день.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Бот для заявок, записи и оплаты — для бизнеса в Саратове. Простой бот запускаю за 1 день.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -7246,7 +7477,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-saratov-bot-b.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-saratov-bot.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7350,29 +7581,34 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Лендинг под ключ за 1–2 дня</t>
+          <t>Лендинг под ключ за 1–2 дня. Макет бесплатно</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>Делаю лендинги и сайты-визитки для бизнеса в Тюмени — удалённо, за 1–2 дня.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Делаю лендинги и сайты-визитки для бизнеса в Тюмени — удалённо, за 1–2 дня.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -7384,7 +7620,7 @@
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-018-b.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-018.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7484,29 +7720,34 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка под ключ</t>
+          <t>Сайт-визитка за 1–2 дня. Макет бесплатно</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>Одностраничный сайт под рекламу и соцсети — для бизнеса в Тольятти и по всей России.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Одностраничный сайт под рекламу и соцсети — для бизнеса в Тольятти и по всей России.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -7518,7 +7759,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-tolyatti-vizitka.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-tolyatti-vizitka.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7626,34 +7867,36 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Разработка сайта под ключ за 1–2 дня</t>
+          <t>Разработка сайтов: сначала макет, потом оплата</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>Работаю с заказчиками в Ижевске онлайн: смета и срок — в первый день.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Работаю с заказчиками в Ижевске онлайн: смета и срок — в первый день.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -7665,7 +7908,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-izhevsk-sayt-b.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-izhevsk-sayt.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7773,34 +8016,36 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Сайт для компании под ключ</t>
+          <t>Сайт компании под ключ за 3–5 дней</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>Для бизнеса в Барнауле: делаю сайт сам, без офиса и наценки агентства.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Для бизнеса в Барнауле: делаю сайт сам, без офиса и наценки агентства.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -7812,7 +8057,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-barnaul-korp.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-barnaul-korp.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7924,34 +8169,36 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>Сайт под ключ: визитка, лендинг, магазин</t>
+          <t>Интернет-магазин под ключ за 5–7 дней</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>В Ульяновске работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+В Ульяновске работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -7963,7 +8210,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-022.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-022.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8071,34 +8318,36 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Создание сайта для бизнеса под ключ</t>
+          <t>Сайт, который приносит заявки, под ключ</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>Сайты для компаний и частных мастеров в Иркутске — от макета до запуска на вашем домене.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Сайты для компаний и частных мастеров в Иркутске — от макета до запуска на вашем домене.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -8110,7 +8359,7 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-irkutsk-sayt.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-irkutsk-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8210,29 +8459,34 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Создание лендинга под ключ</t>
+          <t>Продающий лендинг под рекламу за 2 дня</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>В Хабаровске работаю удалённо: бриф, макет, запуск — без встреч и поездок.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+В Хабаровске работаю удалённо: бриф, макет, запуск — без встреч и поездок.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -8244,7 +8498,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-habarovsk-lending.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-habarovsk-lending.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8356,34 +8610,36 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Создание и доработка сайтов</t>
+          <t>Создание и доработка сайтов от 1 дня</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>Делаю сайты для бизнеса в Ярославле и по всей России — удалённо, напрямую, без менеджеров.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Делаю сайты для бизнеса в Ярославле и по всей России — удалённо, напрямую, без менеджеров.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -8395,7 +8651,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-024.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-024.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8503,34 +8759,36 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Создание сайта с нуля под ключ</t>
+          <t>Создание сайта с нуля за 1–2 дня</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>Работаю с заказчиками во Владивостоке онлайн: смета и срок — в первый день.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Работаю с заказчиками во Владивостоке онлайн: смета и срок — в первый день.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -8542,7 +8800,7 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-vladivostok-sayt.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-vladivostok-sayt.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8642,29 +8900,34 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка для бизнеса за 1–2 дня</t>
+          <t>Сайт-визитка для бизнеса под ключ</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>Для мастеров и компаний в Махачкале: быстрый сайт, с которого приходят заявки.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Для мастеров и компаний в Махачкале: быстрый сайт, с которого приходят заявки.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -8676,7 +8939,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-mahachkala-vizitka-b.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-mahachkala-vizitka.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8768,30 +9031,37 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Бот для записи клиентов в Telegram</t>
+          <t>Telegram-бот для заказов и оплаты</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>В Томске работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+В Томске работаю удалённо: сценарий согласуем в переписке, бота показываю на тесте.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для агентства недвижимости, онлайн-школы, интернет-магазина, доставки еды, салона красоты.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -8803,7 +9073,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-tomsk-bot.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/4k/15.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/13.jpg | https://ysddev.com/avito/4k/34.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-tomsk-bot.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -8916,29 +9186,31 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>Для бизнеса в Оренбурге: делаю сайт сам, без офиса и наценки агентства.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Для бизнеса в Оренбурге: делаю сайт сам, без офиса и наценки агентства.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -8950,7 +9222,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-orenburg-sayt.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-orenburg-sayt.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9050,29 +9322,34 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Продающий лендинг под ключ</t>
+          <t>Лендинг, который собирает заявки</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>Делаю лендинги и сайты-визитки для бизнеса в Кемерово — удалённо, за 1–2 дня.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Делаю лендинги и сайты-визитки для бизнеса в Кемерово — удалённо, за 1–2 дня.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -9084,7 +9361,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-kemerovo-lending.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-kemerovo-lending.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9184,29 +9461,34 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка и лендинг под ключ</t>
+          <t>Сайт-визитка и лендинг за 1–2 дня</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>Одностраничный сайт под рекламу и соцсети — для бизнеса в Новокузнецке и по всей России.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Одностраничный сайт под рекламу и соцсети — для бизнеса в Новокузнецке и по всей России.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -9218,7 +9500,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-novokuzneck-vizitka.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-novokuzneck-vizitka.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9326,34 +9608,36 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Корпоративный сайт и сайт под ключ</t>
+          <t>Корпоративный сайт под ключ. Макет бесплатно</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>В Рязани работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+В Рязани работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -9365,7 +9649,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-ryazan-korp.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-ryazan-korp.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9473,34 +9757,36 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>Разработка сайтов для бизнеса</t>
+          <t>Разработка сайтов для бизнеса. Макет бесплатно</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>Сайты для компаний и частных мастеров в Набережных Челнах — от макета до запуска на вашем домене.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Сайты для компаний и частных мастеров в Набережных Челнах — от макета до запуска на вашем домене.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -9512,7 +9798,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-naberezhnye-chelny-sayt.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-naberezhnye-chelny-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9612,29 +9898,34 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>Лендинг для рекламы и соцсетей</t>
+          <t>Лендинг для рекламы и соцсетей под ключ</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>В Астрахани работаю удалённо: бриф, макет, запуск — без встреч и поездок.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+В Астрахани работаю удалённо: бриф, макет, запуск — без встреч и поездок.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -9646,7 +9937,7 @@
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-astrahan-lending.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-astrahan-lending.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9754,34 +10045,36 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>Интернет-магазин и сайт под ключ</t>
+          <t>Сайт и интернет-магазин под ключ</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>Делаю сайты для бизнеса в Пензе и по всей России — удалённо, напрямую, без менеджеров.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Делаю сайты для бизнеса в Пензе и по всей России — удалённо, напрямую, без менеджеров.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -9793,7 +10086,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-penza-magazin.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-penza-magazin.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9901,34 +10194,36 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>Сайт под ключ с формой заявок в Telegram</t>
+          <t>Сайт под ключ с заявками в Telegram</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>Работаю с заказчиками в Кирове онлайн: смета и срок — в первый день.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Работаю с заказчиками в Кирове онлайн: смета и срок — в первый день.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -9940,7 +10235,7 @@
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-kirov-sayt.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-kirov-sayt.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10036,30 +10331,37 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>Telegram-бот для заказов и оплаты</t>
+          <t>Бот для записи клиентов в Telegram</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>Делаю Telegram-ботов для бизнеса в Липецке и по всей России — удалённо.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Делаю Telegram-ботов для бизнеса в Липецке и по всей России — удалённо.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для доставки еды, салона красоты, стоматологии, ресторана, автосервиса.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -10071,7 +10373,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-030.jpg | https://ysddev.com/avito/4k/12.jpg | https://ysddev.com/avito/4k/14.jpg | https://ysddev.com/avito/4k/11.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/32.jpg | https://ysddev.com/avito/4k/35.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-030.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -10171,29 +10473,34 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка под ключ</t>
+          <t>Сайт-визитка за 1–2 дня. Макет бесплатно</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>Для мастеров и компаний в Чебоксарах: быстрый сайт, с которого приходят заявки.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Для мастеров и компаний в Чебоксарах: быстрый сайт, с которого приходят заявки.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -10205,7 +10512,7 @@
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-cheboksary-vizitka.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-cheboksary-vizitka.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10313,34 +10620,36 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>Веб-разработчик: сайт под ключ</t>
+          <t>Веб-разработчик: сайт за 1–2 дня под ключ</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>Для бизнеса в Калининграде: делаю сайт сам, без офиса и наценки агентства.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Для бизнеса в Калининграде: делаю сайт сам, без офиса и наценки агентства.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -10352,7 +10661,7 @@
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-kaliningrad-sayt.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-kaliningrad-sayt.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10452,29 +10761,34 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>Одностраничный сайт под ключ</t>
+          <t>Одностраничный сайт за 1–2 дня под ключ</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>Делаю лендинги и сайты-визитки для бизнеса в Туле — удалённо, за 1–2 дня.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Делаю лендинги и сайты-визитки для бизнеса в Туле — удалённо, за 1–2 дня.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -10486,7 +10800,7 @@
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-tula-lending.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-tula-lending.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10594,34 +10908,36 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>Создание и доработка сайтов</t>
+          <t>Создание и доработка сайтов от 1 дня</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>В Курске работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+В Курске работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -10633,7 +10949,7 @@
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-kursk-dorabotka.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-kursk-dorabotka.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10741,34 +11057,36 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>Создание сайтов под ключ</t>
+          <t>Создание сайтов под ключ. Макет бесплатно</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>Сайты для компаний и частных мастеров в Сочи — от макета до запуска на вашем домене.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Сайты для компаний и частных мастеров в Сочи — от макета до запуска на вашем домене.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -10780,7 +11098,7 @@
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-sochi-sayt.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-sochi-sayt.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10888,34 +11206,36 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>Сайт для компании под ключ</t>
+          <t>Сайт компании под ключ за 3–5 дней</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>Делаю сайты для бизнеса в Ставрополе и по всей России — удалённо, напрямую, без менеджеров.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Делаю сайты для бизнеса в Ставрополе и по всей России — удалённо, напрямую, без менеджеров.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -10927,7 +11247,7 @@
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-stavropol-korp.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-stavropol-korp.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11027,29 +11347,34 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка для бизнеса за 1–2 дня</t>
+          <t>Сайт-визитка для бизнеса под ключ</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>Одностраничный сайт под рекламу и соцсети — для бизнеса в Улан-Удэ и по всей России.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Одностраничный сайт под рекламу и соцсети — для бизнеса в Улан-Удэ и по всей России.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -11061,7 +11386,7 @@
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-ulan-ude-vizitka-b.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-ulan-ude-vizitka.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11161,29 +11486,34 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>Лендинг под ключ за 1–2 дня</t>
+          <t>Лендинг под ключ за 1–2 дня. Макет бесплатно</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>В Твери работаю удалённо: бриф, макет, запуск — без встреч и поездок.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+В Твери работаю удалённо: бриф, макет, запуск — без встреч и поездок.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для агентства недвижимости, креативной студии, ресторана, турагентства, фитнес-клуба.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -11195,7 +11525,7 @@
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-tver-lending-b.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-tver-lending.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11287,30 +11617,37 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Чат-бот для бизнеса в Telegram</t>
+          <t>Чат-бот с ИИ для бизнеса в Telegram</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>Бот для заявок, записи и оплаты — для бизнеса в Магнитогорске. Простой бот запускаю за 1 день.
-Бот, который принимает заявки, пока вы заняты. От 4 990 ₽, простой бот — за 1 день.
-ЧТО УМЕЕТ
-Принимает заявки и складывает их в таблицу или CRM
-Записывает клиентов на время и напоминает о визите
-Считает стоимость — калькулятор прямо в чате
-Принимает оплату картой или через СБП
-Рассылает акции по базе клиентов
-Отвечает на частые вопросы сам, сложное передаёт вам
+          <t>Бот, который принимает заявки и записывает клиентов, пока вы заняты. Простой бот — за 1 день. Сценарий согласуем до оплаты.
+Бот для заявок, записи и оплаты — для бизнеса в Магнитогорске. Простой бот запускаю за 1 день.
+ЧТО УМЕЕТ БОТ
+• Принимает заявки и складывает их в таблицу или CRM
+• Записывает клиентов на время и сам напоминает о визите
+• Считает стоимость — калькулятор прямо в чате
+• Принимает оплату картой или через СБП
+• Рассылает акции по базе клиентов
+• Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽
+Бот для заявок и записи — от 4 990 ₽, от 1 дня
 Приём оплаты в боте — от 3 000 ₽
 Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу и документам — от 9 990 ₽
-ПОЧЕМУ БОТ
-Telegram уже стоит у всех клиентов. Бот открывается за секунду, ничего не нужно скачивать. Разработка — дни, а не месяцы.
-Сценарий согласуем до оплаты. Исходный код и доступы — ваши.
-Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, что бот должен делать — покажу похожие примеры.
+Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+КАК РАБОТАЮ
+1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
+2. Согласуем сценарий до оплаты
+3. Показываю бота на тесте, вносим правки
+4. Запускаю на сервере — бот работает круглосуточно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору
+• Исходный код и доступы — ваши
+Делал ботов для ресторана, автосервиса, турагентства, агентства недвижимости, онлайн-школы.
+Напишите в сообщения слово «Бот» — покажу похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -11322,7 +11659,7 @@
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-magnitogorsk-ai.jpg | https://ysddev.com/avito/4k/38.jpg | https://ysddev.com/avito/4k/39.jpg | https://ysddev.com/avito/4k/56.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/4k/57.jpg | https://ysddev.com/avito/4k/33.jpg | https://ysddev.com/avito/4k/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-magnitogorsk-ai.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -11430,34 +11767,36 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>Сайт под ключ — макет до оплаты</t>
+          <t>Сайт для бизнеса за 1–2 дня под ключ</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>Работаю с заказчиками в Иванове онлайн: смета и срок — в первый день.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Работаю с заказчиками в Иванове онлайн: смета и срок — в первый день.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -11469,7 +11808,7 @@
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-ivanovo-sayt.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-ivanovo-sayt.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11577,34 +11916,36 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Вёрстка и создание сайтов под ключ</t>
+          <t>Вёрстка из Figma и сайты под ключ</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>Для бизнеса в Брянске: делаю сайт сам, без офиса и наценки агентства.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Для бизнеса в Брянске: делаю сайт сам, без офиса и наценки агентства.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -11616,7 +11957,7 @@
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-bryansk-figma.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-bryansk-figma.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11724,34 +12065,36 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Разработка сайта под ключ за 1–2 дня</t>
+          <t>Разработка сайтов: сначала макет, потом оплата</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>В Белгороде работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+В Белгороде работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -11763,7 +12106,7 @@
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-belgorod-sayt-b.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-belgorod-sayt.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11871,34 +12214,36 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Сайт под ключ: визитка, лендинг, магазин</t>
+          <t>Интернет-магазин под ключ за 5–7 дней</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>Сайты для компаний и частных мастеров во Владимире — от макета до запуска на вашем домене.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Сайты для компаний и частных мастеров во Владимире — от макета до запуска на вашем домене.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -11910,7 +12255,7 @@
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-vladimir-magazin.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-vladimir-magazin.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12018,34 +12363,36 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>Создание сайта для бизнеса под ключ</t>
+          <t>Сайт, который приносит заявки, под ключ</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>Делаю сайты для бизнеса в Сургуте и по всей России — удалённо, напрямую, без менеджеров.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Делаю сайты для бизнеса в Сургуте и по всей России — удалённо, напрямую, без менеджеров.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -12057,7 +12404,7 @@
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-surgut-sayt.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-surgut-sayt.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12165,34 +12512,36 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>Создание сайта с нуля под ключ</t>
+          <t>Создание сайта с нуля за 1–2 дня</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>Работаю с заказчиками в Архангельске онлайн: смета и срок — в первый день.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Работаю с заказчиками в Архангельске онлайн: смета и срок — в первый день.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -12204,7 +12553,7 @@
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-arhangelsk-sayt.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-arhangelsk-sayt.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12304,29 +12653,34 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>Создание лендинга под ключ</t>
+          <t>Продающий лендинг под рекламу за 2 дня</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>Для мастеров и компаний в Чите: быстрый сайт, с которого приходят заявки.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Для мастеров и компаний в Чите: быстрый сайт, с которого приходят заявки.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для турагентства, фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -12338,7 +12692,7 @@
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-chita-lending.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-chita-lending.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12451,29 +12805,31 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>Для бизнеса в Калуге: делаю сайт сам, без офиса и наценки агентства.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Для бизнеса в Калуге: делаю сайт сам, без офиса и наценки агентства.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -12485,7 +12841,7 @@
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-kaluga-sayt.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-kaluga-sayt.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12585,29 +12941,34 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка и лендинг под ключ</t>
+          <t>Сайт-визитка и лендинг за 1–2 дня</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>Делаю лендинги и сайты-визитки для бизнеса в Смоленске — удалённо, за 1–2 дня.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Делаю лендинги и сайты-визитки для бизнеса в Смоленске — удалённо, за 1–2 дня.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для ремонта квартир, детейлинг-студии, агентства недвижимости, креативной студии, ресторана.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -12619,7 +12980,7 @@
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-smolensk-vizitka.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-smolensk-vizitka.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12727,34 +13088,36 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>Разработка сайтов для бизнеса</t>
+          <t>Разработка сайтов для бизнеса. Макет бесплатно</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>В Якутске работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+В Якутске работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -12766,7 +13129,7 @@
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-yakutsk-sayt.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-yakutsk-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12874,34 +13237,36 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>Сайт под ключ с формой заявок в Telegram</t>
+          <t>Сайт под ключ с заявками в Telegram</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>Сайты для компаний и частных мастеров в Саранске — от макета до запуска на вашем домене.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Сайты для компаний и частных мастеров в Саранске — от макета до запуска на вашем домене.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -12913,7 +13278,7 @@
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-saransk-sayt.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-saransk-sayt.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13021,34 +13386,36 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>Веб-разработчик: сайт под ключ</t>
+          <t>Веб-разработчик: сайт за 1–2 дня под ключ</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>Делаю сайты для бизнеса в Вологде и по всей России — удалённо, напрямую, без менеджеров.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Делаю сайты для бизнеса в Вологде и по всей России — удалённо, напрямую, без менеджеров.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -13060,7 +13427,7 @@
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-vologda-sayt.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-vologda-sayt.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13160,29 +13527,34 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>Продающий лендинг под ключ</t>
+          <t>Лендинг, который собирает заявки</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>Одностраничный сайт под рекламу и соцсети — для бизнеса в Кургане и по всей России.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Одностраничный сайт под рекламу и соцсети — для бизнеса в Кургане и по всей России.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для креативной студии, ресторана, турагентства, фитнес-клуба, строительной компании.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -13194,7 +13566,7 @@
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-kurgan-lending.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-kurgan-lending.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13302,34 +13674,36 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>Создание сайтов под ключ</t>
+          <t>Создание сайтов под ключ. Макет бесплатно</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>Работаю с заказчиками в Орле онлайн: смета и срок — в первый день.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Работаю с заказчиками в Орле онлайн: смета и срок — в первый день.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -13341,7 +13715,7 @@
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-orel-sayt.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-orel-sayt.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13441,29 +13815,34 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка под ключ</t>
+          <t>Сайт-визитка за 1–2 дня. Макет бесплатно</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>Во Владикавказе работаю удалённо: бриф, макет, запуск — без встреч и поездок.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Во Владикавказе работаю удалённо: бриф, макет, запуск — без встреч и поездок.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для фитнес-клуба, строительной компании, ремонта квартир, детейлинг-студии, агентства недвижимости.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -13475,7 +13854,7 @@
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-vladikavkaz-vizitka.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-vladikavkaz-vizitka.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13583,34 +13962,36 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>Сайт под ключ — макет до оплаты</t>
+          <t>Сайт для бизнеса за 1–2 дня под ключ</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>Для бизнеса в Мурманске: делаю сайт сам, без офиса и наценки агентства.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Для бизнеса в Мурманске: делаю сайт сам, без офиса и наценки агентства.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -13622,7 +14003,7 @@
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-murmansk-sayt.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-murmansk-sayt.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13730,34 +14111,36 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>Разработка сайта под ключ за 1–2 дня</t>
+          <t>Разработка сайтов: сначала макет, потом оплата</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>В Тамбове работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+В Тамбове работаю удалённо — встречи не нужны, всё решаем в переписке или по телефону.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для онлайн-школы, агентства недвижимости, детейлинг-студии, ресторана, стоматологии.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -13769,7 +14152,7 @@
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-tambov-sayt-b.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-tambov-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13877,34 +14260,36 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>Создание сайта для бизнеса под ключ</t>
+          <t>Сайт, который приносит заявки, под ключ</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>Сайты для компаний и частных мастеров в Петрозаводске — от макета до запуска на вашем домене.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Сайты для компаний и частных мастеров в Петрозаводске — от макета до запуска на вашем домене.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для ресторана, стоматологии, салона красоты, юридической фирмы, строительной компании.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -13916,7 +14301,7 @@
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-petrozavodsk-sayt.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-petrozavodsk-sayt.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14016,29 +14401,34 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>Лендинг для рекламы и соцсетей</t>
+          <t>Лендинг для рекламы и соцсетей под ключ</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>Для мастеров и компаний в Костроме: быстрый сайт, с которого приходят заявки.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Для мастеров и компаний в Костроме: быстрый сайт, с которого приходят заявки.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для детейлинг-студии, агентства недвижимости, креативной студии, ресторана, турагентства.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -14050,7 +14440,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-kostroma-lending.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/30.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-kostroma-lending.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14158,34 +14548,36 @@
       </c>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>Создание сайта с нуля под ключ</t>
+          <t>Создание сайта с нуля за 1–2 дня</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>Делаю сайты для бизнеса в Йошкар-Оле и по всей России — удалённо, напрямую, без менеджеров.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Делаю сайты для бизнеса в Йошкар-Оле и по всей России — удалённо, напрямую, без менеджеров.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для юридической фирмы, строительной компании, фитнес-клуба, турагентства, магазина мебели.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -14197,7 +14589,7 @@
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-yoshkar-ola-sayt.jpg | https://ysddev.com/avito/4k/36.jpg | https://ysddev.com/avito/4k/37.jpg | https://ysddev.com/avito/4k/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/55.jpg | https://ysddev.com/avito/4k/24.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-yoshkar-ola-sayt.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14297,29 +14689,34 @@
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>Сайт-визитка для бизнеса за 1–2 дня</t>
+          <t>Сайт-визитка для бизнеса под ключ</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>Делаю лендинги и сайты-визитки для бизнеса в Сыктывкаре — удалённо, за 1–2 дня.
-Одностраничный сайт под одну услугу, который собирает заявки. От 4 990 ₽, 1–2 дня.
-ЧТО ВХОДИТ
-Структура: что за чем идёт, чтобы человек дочитал и написал
-Дизайн под ваш продукт, без шаблонной «рыбы»
-Помогу с текстами по вашим вводным
-Форма заявки с уведомлением в Telegram или на почту
-Адаптив: телефон, планшет, компьютер
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
+          <t>Лендинг, который превращает рекламу в заявки, — за 1–2 дня. Сначала бесплатный макет, оплата — только если понравится.
+Делаю лендинги и сайты-визитки для бизнеса в Сыктывкаре — удалённо, за 1–2 дня.
+ЧТО ПОЛУЧИТЕ
+• Одна страница под одну услугу — человек дочитывает и оставляет заявку
+• Дизайн под ваш продукт, не шаблон; помогу с текстами
+• Заявки сразу приходят вам в Telegram или на почту
+• Удобно с телефона и готово под рекламу в Директе и соцсетях
+• Домен, хостинг, SSL и Яндекс Метрика с целями
+ЦЕНА И СРОК
+Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
-Короткий бриф — смета и срок в тот же день — макет первого экрана до оплаты — сборка — правки — запуск на вашем домене. Показываю результат каждый день.
-НУЖНО БОЛЬШЕ СТРАНИЦ
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-14 дней правок после сдачи бесплатно. Исходники и доступы остаются у вас.
-Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Расскажите в сообщениях, что продаёте и кому — посчитаю точно.
+1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю страницу и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена не растёт
+• Исходники и доступы остаются у вас
+Делал лендинги для ресторана, турагентства, фитнес-клуба, строительной компании, ремонта квартир.
+Напишите в сообщения слово «Лендинг» — пришлю похожие примеры и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -14331,7 +14728,7 @@
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-syktyvkar-vizitka-b.jpg | https://ysddev.com/avito/4k/31.jpg | https://ysddev.com/avito/4k/21.jpg | https://ysddev.com/avito/4k/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/20.jpg | https://ysddev.com/avito/4k/27.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-syktyvkar-vizitka.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14444,29 +14841,31 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>Работаю с заказчиками в Новороссийске онлайн: смета и срок — в первый день.
-Соберу сайт, с которого пишут и звонят. Первый макет — до оплаты: не понравится, разойдёмся без обид.
+          <t>Сделаю сайт, с которого вам пишут и звонят. Сначала бесплатный макет — платите, только если понравится.
+Работаю с заказчиками в Новороссийске онлайн: смета и срок — в первый день.
+ЧТО ПОЛУЧИТЕ
+• Сайт под ваш бизнес: визитка или лендинг за 1–2 дня, сайт компании за 3–5 дней
+• Заявки с сайта сразу приходят вам в Telegram
+• Удобно с телефона — большинство клиентов заходят именно с него
+• Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
+• Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
 Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
 Доработка готового сайта — от 1 000 ₽, от 1 дня
-Смету называю в первый день, дальше она не меняется. Срочные беру.
-ЧТО ВХОДИТ
-Структура и дизайн под вашу задачу, не шаблон
-Вёрстка под телефон и планшет
-Форма заявки с уведомлением вам в Telegram
-Базовое SEO: заголовки, описания, карта сайта, скорость
-Подключение домена, хостинга и SSL
-Яндекс Метрика с целями
-Обучение: тексты и цены меняете сами
-ГАРАНТИИ
-Макет до оплаты
-Цена из сметы не растёт
-14 дней правок после сдачи бесплатно (на магазин — 60)
-Исходники, доступы и домен остаются у вас
-Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости. В портфолио 63 работы — часть на фото, остальные пришлю в переписке.
-Напишите в сообщения, чем занимаетесь и какой нужен сайт — отвечу быстро и назову точную цену.
+КАК РАБОТАЮ
+1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
+2. Делаю макет первого экрана — бесплатно
+3. Нравится — собираю сайт и показываю результат каждый день
+4. Запускаю на вашем домене, 14 дней правок бесплатно
+ПОЧЕМУ МНЕ ДОВЕРЯЮТ
+• 63 работы в портфолио — часть на фото, остальные пришлю в переписке
+• Делаю сам, без менеджеров и наценки агентства
+• Работаю по договору, цена из сметы не растёт
+• Исходники, доступы и домен остаются у вас
+Делал сайты для турагентства, магазина мебели, логистической компании, онлайн-школы, агентства недвижимости.
+Напишите в сообщения слово «Сайт» — пришлю похожие примеры под вашу нишу и назову точную цену.
 Почему дешевле студий: работаю сам, без офиса и менеджеров — вы не платите за агентство. Работаю по договору, без предоплаты за макет.
 Работаю удалённо по всей России: обсуждаем всё в переписке или по телефону, ехать никуда не нужно.</t>
         </is>
@@ -14478,7 +14877,7 @@
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c/ysd-novorossiysk-sayt.jpg | https://ysddev.com/avito/4k/25.jpg | https://ysddev.com/avito/4k/18.jpg | https://ysddev.com/avito/4k/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/4k/28.jpg | https://ysddev.com/avito/4k/22.jpg | https://ysddev.com/avito/4k/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c2/ysd-novorossiysk-sayt.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -697,10 +697,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -719,12 +719,12 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-moskva-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-moskva-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -858,12 +858,12 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-moskva-lending-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-moskva-lending-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -970,10 +970,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -992,12 +992,12 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-moskva-bot-2.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-moskva-bot-2.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -1131,12 +1131,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-sankt-peterburg-lending.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-sankt-peterburg-lending.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1258,10 +1258,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -1280,12 +1280,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-sankt-peterburg-sayt-2.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-sankt-peterburg-sayt-2.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1392,10 +1392,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -1414,12 +1414,12 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-sankt-peterburg-bot-2.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-sankt-peterburg-bot-2.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1541,10 +1541,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -1563,12 +1563,12 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-novosibirsk-magazin.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-novosibirsk-magazin.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -1702,12 +1702,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-novosibirsk-lending-2.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-novosibirsk-lending-2.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1814,10 +1814,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -1836,12 +1836,12 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-novosibirsk-bot-2.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-novosibirsk-bot-2.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1967,10 +1967,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -1989,12 +1989,12 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-004.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-004.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -2128,12 +2128,12 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-ekaterinburg-vizitka-2.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-ekaterinburg-vizitka-2.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2240,10 +2240,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -2262,12 +2262,12 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-ekaterinburg-bot-2.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-ekaterinburg-bot-2.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2393,10 +2393,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -2415,12 +2415,12 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/8253207537.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/8253207537.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -2554,12 +2554,12 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-kazan-lending-2.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-kazan-lending-2.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2666,10 +2666,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -2688,12 +2688,12 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-kazan-bot-2.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-kazan-bot-2.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2815,10 +2815,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -2837,12 +2837,12 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-nizhniy-novgorod-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-nizhniy-novgorod-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -2976,12 +2976,12 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-nizhniy-novgorod-vizitka-2.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-nizhniy-novgorod-vizitka-2.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -3110,12 +3110,12 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-nizhniy-novgorod-bot-2.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-nizhniy-novgorod-bot-2.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3241,10 +3241,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -3263,12 +3263,12 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-012.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-012.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -3402,12 +3402,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-krasnoyarsk-lending-2.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-krasnoyarsk-lending-2.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3514,10 +3514,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -3536,12 +3536,12 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-krasnoyarsk-bot-2.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-krasnoyarsk-bot-2.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3648,10 +3648,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -3670,12 +3670,12 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-chelyabinsk-bot.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-chelyabinsk-bot.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3797,10 +3797,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -3819,12 +3819,12 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-chelyabinsk-sayt-2.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-chelyabinsk-sayt-2.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -3958,12 +3958,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-chelyabinsk-vizitka-2.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-chelyabinsk-vizitka-2.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4077,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -4097,12 +4097,12 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-samara-lending.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-samara-lending.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4224,10 +4224,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -4246,12 +4246,12 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-samara-sayt-2.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-samara-sayt-2.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4358,10 +4358,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -4380,12 +4380,12 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-samara-bot-2.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-samara-bot-2.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4496,10 +4496,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -4518,12 +4518,12 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-011.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-011.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4645,10 +4645,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -4667,12 +4667,12 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-ufa-sayt-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-ufa-sayt-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -4806,12 +4806,12 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-ufa-vizitka-2.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-ufa-vizitka-2.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4933,10 +4933,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -4955,12 +4955,12 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-rostov-na-donu-korp.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-rostov-na-donu-korp.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -5094,12 +5094,12 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-rostov-na-donu-lending-2.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-rostov-na-donu-lending-2.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5206,10 +5206,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -5228,12 +5228,12 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-rostov-na-donu-bot-2.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-rostov-na-donu-bot-2.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5355,10 +5355,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -5377,12 +5377,12 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-krasnodar-sayt.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-krasnodar-sayt.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -5516,12 +5516,12 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-krasnodar-vizitka-2.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-krasnodar-vizitka-2.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5628,10 +5628,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -5650,12 +5650,12 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-krasnodar-bot-2.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-krasnodar-bot-2.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5777,10 +5777,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -5799,12 +5799,12 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-omsk-sayt.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-omsk-sayt.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -5938,12 +5938,12 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-omsk-lending-2.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-omsk-lending-2.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6050,10 +6050,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -6072,12 +6072,12 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-omsk-bot-2.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-omsk-bot-2.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6199,10 +6199,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -6221,12 +6221,12 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-voronezh-sayt.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-voronezh-sayt.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6340,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -6360,12 +6360,12 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-voronezh-vizitka-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-voronezh-vizitka-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6472,10 +6472,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -6494,12 +6494,12 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-voronezh-bot-2.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-voronezh-bot-2.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6621,10 +6621,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -6643,12 +6643,12 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-perm-magazin.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-perm-magazin.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -6782,12 +6782,12 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-perm-lending-2.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-perm-lending-2.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6894,10 +6894,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -6916,12 +6916,12 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-perm-bot-2.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-perm-bot-2.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -7055,12 +7055,12 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-volgograd-lending.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-volgograd-lending.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7182,10 +7182,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -7204,12 +7204,12 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-volgograd-sayt-2.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-volgograd-sayt-2.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7316,10 +7316,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -7338,12 +7338,12 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-volgograd-bot-2.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-volgograd-bot-2.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7450,10 +7450,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -7472,12 +7472,12 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-saratov-bot.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-saratov-bot.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7595,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -7615,12 +7615,12 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-018.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-018.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -7754,12 +7754,12 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-tolyatti-vizitka.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-tolyatti-vizitka.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7881,10 +7881,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -7903,12 +7903,12 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-izhevsk-sayt.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-izhevsk-sayt.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8030,10 +8030,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8052,12 +8052,12 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-barnaul-korp.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-barnaul-korp.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8183,10 +8183,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8205,12 +8205,12 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-022.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-022.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8332,10 +8332,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8354,12 +8354,12 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-irkutsk-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-irkutsk-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -8493,12 +8493,12 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-habarovsk-lending.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-habarovsk-lending.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8624,10 +8624,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8646,12 +8646,12 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-024.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-024.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8773,10 +8773,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8795,12 +8795,12 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-vladivostok-sayt.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-vladivostok-sayt.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -8934,12 +8934,12 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-mahachkala-vizitka.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-mahachkala-vizitka.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9046,10 +9046,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -9068,12 +9068,12 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-tomsk-bot.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-tomsk-bot.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -9195,10 +9195,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -9217,12 +9217,12 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-orenburg-sayt.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-orenburg-sayt.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -9356,12 +9356,12 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-kemerovo-lending.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-kemerovo-lending.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -9495,12 +9495,12 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-novokuzneck-vizitka.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-novokuzneck-vizitka.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9622,10 +9622,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -9644,12 +9644,12 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-ryazan-korp.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-ryazan-korp.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9771,10 +9771,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -9793,12 +9793,12 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-naberezhnye-chelny-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-naberezhnye-chelny-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9912,7 +9912,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -9932,12 +9932,12 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-astrahan-lending.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-astrahan-lending.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10059,10 +10059,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -10081,12 +10081,12 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-penza-magazin.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-penza-magazin.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10208,10 +10208,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -10230,12 +10230,12 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-kirov-sayt.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-kirov-sayt.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10346,10 +10346,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -10368,12 +10368,12 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-030.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-030.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -10487,7 +10487,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -10507,12 +10507,12 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-cheboksary-vizitka.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-cheboksary-vizitka.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10634,10 +10634,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -10656,12 +10656,12 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-kaliningrad-sayt.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-kaliningrad-sayt.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -10795,12 +10795,12 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-tula-lending.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-tula-lending.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10922,10 +10922,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -10944,12 +10944,12 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-kursk-dorabotka.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-kursk-dorabotka.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11071,10 +11071,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -11093,12 +11093,12 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-sochi-sayt.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-sochi-sayt.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11220,10 +11220,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -11242,12 +11242,12 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-stavropol-korp.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-stavropol-korp.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -11381,12 +11381,12 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-ulan-ude-vizitka.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-ulan-ude-vizitka.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11500,7 +11500,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -11520,12 +11520,12 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-tver-lending.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-tver-lending.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11632,10 +11632,10 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 4 990 ₽, от 1 дня
-Приём оплаты в боте — от 3 000 ₽
-Выгрузка в Google Таблицы или CRM — от 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 9 990 ₽
+Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Приём оплаты в боте — плюс 3 000 ₽
+Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -11654,12 +11654,12 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-magnitogorsk-ai.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-4h.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-magnitogorsk-ai.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -11781,10 +11781,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -11803,12 +11803,12 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-ivanovo-sayt.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-ivanovo-sayt.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11930,10 +11930,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -11952,12 +11952,12 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-bryansk-figma.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-bryansk-figma.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12079,10 +12079,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12101,12 +12101,12 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-belgorod-sayt.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-belgorod-sayt.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12228,10 +12228,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12250,12 +12250,12 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-vladimir-magazin.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-vladimir-magazin.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12377,10 +12377,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12399,12 +12399,12 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-surgut-sayt.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-surgut-sayt.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12526,10 +12526,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12548,12 +12548,12 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-arhangelsk-sayt.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-arhangelsk-sayt.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -12687,12 +12687,12 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-chita-lending.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-chita-lending.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12814,10 +12814,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12836,12 +12836,12 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-kaluga-sayt.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-kaluga-sayt.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -12975,12 +12975,12 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-smolensk-vizitka.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-smolensk-vizitka.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13102,10 +13102,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13124,12 +13124,12 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-yakutsk-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-yakutsk-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13251,10 +13251,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13273,12 +13273,12 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-saransk-sayt.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-saransk-sayt.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13400,10 +13400,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13422,12 +13422,12 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-vologda-sayt.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-vologda-sayt.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -13561,12 +13561,12 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-kurgan-lending.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-kurgan-lending.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13688,10 +13688,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13710,12 +13710,12 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-orel-sayt.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-orel-sayt.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -13849,12 +13849,12 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-vladikavkaz-vizitka.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-vladikavkaz-vizitka.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13976,10 +13976,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13998,12 +13998,12 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-murmansk-sayt.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-murmansk-sayt.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14125,10 +14125,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -14147,12 +14147,12 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-tambov-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-tambov-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14274,10 +14274,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -14296,12 +14296,12 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-petrozavodsk-sayt.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-petrozavodsk-sayt.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14415,7 +14415,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -14435,12 +14435,12 @@
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-kostroma-lending.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-kostroma-lending.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14562,10 +14562,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -14584,12 +14584,12 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-yoshkar-ola-sayt.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-yoshkar-ola-sayt.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14703,7 +14703,7 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 4 990 ₽, 1–2 дня
+Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
 Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
@@ -14723,12 +14723,12 @@
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-syktyvkar-vizitka.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-syktyvkar-vizitka.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14850,10 +14850,10 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 4 990 ₽, 1–2 дня
+Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
 Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
 Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — от 1 000 ₽, от 1 дня
+Доработка готового сайта — цену назову после просмотра
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -14872,12 +14872,12 @@
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c2/ysd-novorossiysk-sayt.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4h.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c3/ysd-novorossiysk-sayt.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>

--- a/avito/ysddev-avito.xlsx
+++ b/avito/ysddev-avito.xlsx
@@ -697,10 +697,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -719,12 +720,12 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-moskva-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-moskva-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -838,8 +839,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -858,12 +860,12 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-moskva-lending-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-moskva-lending-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -970,10 +972,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -992,12 +995,12 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-moskva-bot-2.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-moskva-bot-2.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1111,8 +1114,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -1131,12 +1135,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-sankt-peterburg-lending.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-sankt-peterburg-lending.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1258,10 +1262,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -1280,12 +1285,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-sankt-peterburg-sayt-2.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-sankt-peterburg-sayt-2.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1392,10 +1397,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -1414,12 +1420,12 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-sankt-peterburg-bot-2.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-sankt-peterburg-bot-2.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1541,10 +1547,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -1563,12 +1570,12 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-novosibirsk-magazin.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-novosibirsk-magazin.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1682,8 +1689,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -1702,12 +1710,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-novosibirsk-lending-2.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-novosibirsk-lending-2.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -1814,10 +1822,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -1836,12 +1845,12 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-novosibirsk-bot-2.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-novosibirsk-bot-2.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -1967,10 +1976,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -1989,12 +1999,12 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-004.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-004.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2108,8 +2118,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -2128,12 +2139,12 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-ekaterinburg-vizitka-2.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-ekaterinburg-vizitka-2.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2240,10 +2251,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -2262,12 +2274,12 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-ekaterinburg-bot-2.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-ekaterinburg-bot-2.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2393,10 +2405,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -2415,12 +2428,12 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/8253207537.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/8253207537.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2534,8 +2547,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -2554,12 +2568,12 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-kazan-lending-2.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-kazan-lending-2.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2666,10 +2680,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -2688,12 +2703,12 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-kazan-bot-2.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-kazan-bot-2.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -2815,10 +2830,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -2837,12 +2853,12 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-nizhniy-novgorod-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-nizhniy-novgorod-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -2956,8 +2972,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -2976,12 +2993,12 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-nizhniy-novgorod-vizitka-2.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-nizhniy-novgorod-vizitka-2.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3105,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -3110,12 +3128,12 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-nizhniy-novgorod-bot-2.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-nizhniy-novgorod-bot-2.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3241,10 +3259,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -3263,12 +3282,12 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-012.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-012.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3382,8 +3401,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -3402,12 +3422,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-krasnoyarsk-lending-2.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-krasnoyarsk-lending-2.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3514,10 +3534,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -3536,12 +3557,12 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-krasnoyarsk-bot-2.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-krasnoyarsk-bot-2.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3648,10 +3669,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -3670,12 +3692,12 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-chelyabinsk-bot.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-chelyabinsk-bot.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -3797,10 +3819,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -3819,12 +3842,12 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-chelyabinsk-sayt-2.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-chelyabinsk-sayt-2.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -3938,8 +3961,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -3958,12 +3982,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-chelyabinsk-vizitka-2.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-chelyabinsk-vizitka-2.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4077,8 +4101,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -4097,12 +4122,12 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-samara-lending.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-samara-lending.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4224,10 +4249,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -4251,7 +4277,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-samara-sayt-2.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-samara-sayt-2.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4358,10 +4384,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -4380,12 +4407,12 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-samara-bot-2.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-samara-bot-2.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4496,10 +4523,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -4523,7 +4551,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-011.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-011.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -4645,10 +4673,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -4667,12 +4696,12 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-ufa-sayt-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-ufa-sayt-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4786,8 +4815,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -4806,12 +4836,12 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-ufa-vizitka-2.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-ufa-vizitka-2.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -4933,10 +4963,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -4955,12 +4986,12 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-rostov-na-donu-korp.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-rostov-na-donu-korp.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5074,8 +5105,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -5094,12 +5126,12 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-rostov-na-donu-lending-2.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-rostov-na-donu-lending-2.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5206,10 +5238,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -5228,12 +5261,12 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-rostov-na-donu-bot-2.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-rostov-na-donu-bot-2.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5355,10 +5388,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -5377,12 +5411,12 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-krasnodar-sayt.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-krasnodar-sayt.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5496,8 +5530,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -5516,12 +5551,12 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-krasnodar-vizitka-2.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-krasnodar-vizitka-2.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5628,10 +5663,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -5650,12 +5686,12 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-krasnodar-bot-2.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-krasnodar-bot-2.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -5777,10 +5813,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -5799,12 +5836,12 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-omsk-sayt.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-omsk-sayt.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -5918,8 +5955,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -5938,12 +5976,12 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-omsk-lending-2.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-omsk-lending-2.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6050,10 +6088,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -6072,12 +6111,12 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-omsk-bot-2.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-omsk-bot-2.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6199,10 +6238,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -6221,12 +6261,12 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-voronezh-sayt.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-voronezh-sayt.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6340,8 +6380,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -6360,12 +6401,12 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-voronezh-vizitka-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-voronezh-vizitka-2.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6472,10 +6513,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -6494,12 +6536,12 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-voronezh-bot-2.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-voronezh-bot-2.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -6621,10 +6663,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -6648,7 +6691,7 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-perm-magazin.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-perm-magazin.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6762,8 +6805,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -6782,12 +6826,12 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-perm-lending-2.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-perm-lending-2.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -6894,10 +6938,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -6916,12 +6961,12 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-perm-bot-2.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-perm-bot-2.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7035,8 +7080,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -7055,12 +7101,12 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-volgograd-lending.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-volgograd-lending.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7182,10 +7228,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -7204,12 +7251,12 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-volgograd-sayt-2.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-volgograd-sayt-2.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7316,10 +7363,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -7338,12 +7386,12 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-volgograd-bot-2.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-volgograd-bot-2.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7450,10 +7498,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -7472,12 +7521,12 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-saratov-bot.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-saratov-bot.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -7595,8 +7644,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -7615,12 +7665,12 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-018.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-018.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7734,8 +7784,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -7754,12 +7805,12 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-tolyatti-vizitka.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-tolyatti-vizitka.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -7881,10 +7932,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -7903,12 +7955,12 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-izhevsk-sayt.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-izhevsk-sayt.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8030,10 +8082,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8052,12 +8105,12 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-barnaul-korp.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-barnaul-korp.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8183,10 +8236,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8205,12 +8259,12 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-022.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-022.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8332,10 +8386,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8354,12 +8409,12 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-irkutsk-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-irkutsk-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8473,8 +8528,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8493,12 +8549,12 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-habarovsk-lending.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-habarovsk-lending.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8624,10 +8680,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8646,12 +8703,12 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-024.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-024.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8773,10 +8830,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8795,12 +8853,12 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-vladivostok-sayt.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-vladivostok-sayt.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -8914,8 +8972,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -8934,12 +8993,12 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-mahachkala-vizitka.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-mahachkala-vizitka.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9046,10 +9105,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -9068,12 +9128,12 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-tomsk-bot.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-tomsk-bot.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/w4/15.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/13.jpg | https://ysddev.com/avito/w4/34.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -9195,10 +9255,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -9222,7 +9283,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-orenburg-sayt.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-orenburg-sayt.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9336,8 +9397,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -9356,12 +9418,12 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-kemerovo-lending.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-kemerovo-lending.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9475,8 +9537,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -9495,12 +9558,12 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-novokuzneck-vizitka.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-novokuzneck-vizitka.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9622,10 +9685,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -9644,12 +9708,12 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-ryazan-korp.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-ryazan-korp.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9771,10 +9835,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -9793,12 +9858,12 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-naberezhnye-chelny-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-naberezhnye-chelny-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -9912,8 +9977,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -9932,12 +9998,12 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-astrahan-lending.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-astrahan-lending.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10059,10 +10125,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -10086,7 +10153,7 @@
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-penza-magazin.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-penza-magazin.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10208,10 +10275,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -10230,12 +10298,12 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-kirov-sayt.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-kirov-sayt.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10346,10 +10414,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -10368,12 +10437,12 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-030.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-030.jpg | https://ysddev.com/avito/w4/12.jpg | https://ysddev.com/avito/w4/14.jpg | https://ysddev.com/avito/w4/11.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/32.jpg | https://ysddev.com/avito/w4/35.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -10487,8 +10556,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -10507,12 +10577,12 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-cheboksary-vizitka.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-cheboksary-vizitka.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10634,10 +10704,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -10656,12 +10727,12 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-kaliningrad-sayt.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-kaliningrad-sayt.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10775,8 +10846,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -10795,12 +10867,12 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-tula-lending.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-tula-lending.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -10922,10 +10994,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -10944,12 +11017,12 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-kursk-dorabotka.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-kursk-dorabotka.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11071,10 +11144,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -11093,12 +11167,12 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-sochi-sayt.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-sochi-sayt.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11220,10 +11294,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -11242,12 +11317,12 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-stavropol-korp.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-stavropol-korp.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11361,8 +11436,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -11381,12 +11457,12 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-ulan-ude-vizitka.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-ulan-ude-vizitka.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11500,8 +11576,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -11520,12 +11597,12 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-tver-lending.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-tver-lending.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11632,10 +11709,11 @@
 • Рассылает акции по базе клиентов
 • Отвечает на частые вопросы, сложное передаёт вам
 ЦЕНЫ
-Бот для заявок и записи — от 10 000 ₽, от 1 дня
+Бот для заявок и записи — от 8 000 ₽, от 1 дня
 Приём оплаты в боте — плюс 3 000 ₽
 Выгрузка в Google Таблицы или CRM — плюс 1 500 ₽
-Бот с ИИ, который отвечает по вашему прайсу, — от 14 990 ₽
+Бот с ИИ, который отвечает по вашему прайсу, — от 10 000 ₽
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Рассказываете, что должен делать бот, — в тот же день называю цену и срок
 2. Согласуем сценарий до оплаты
@@ -11659,7 +11737,7 @@
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-magnitogorsk-ai.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-4p.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-magnitogorsk-ai.jpg | https://ysddev.com/avito/w4/38.jpg | https://ysddev.com/avito/w4/39.jpg | https://ysddev.com/avito/w4/56.jpg | https://ysddev.com/avito/bot-5p.jpg | https://ysddev.com/avito/w4/57.jpg | https://ysddev.com/avito/w4/33.jpg | https://ysddev.com/avito/w4/16.jpg | https://ysddev.com/avito/bot-info-1h.jpg | https://ysddev.com/avito/bot-info-2h.jpg</t>
         </is>
       </c>
     </row>
@@ -11781,10 +11859,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -11803,12 +11882,12 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-ivanovo-sayt.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-ivanovo-sayt.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -11930,10 +12009,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -11952,12 +12032,12 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-bryansk-figma.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-bryansk-figma.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12079,10 +12159,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12101,12 +12182,12 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-belgorod-sayt.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-belgorod-sayt.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12228,10 +12309,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12250,12 +12332,12 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-vladimir-magazin.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-vladimir-magazin.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12377,10 +12459,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12399,12 +12482,12 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-surgut-sayt.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-surgut-sayt.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12526,10 +12609,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12548,12 +12632,12 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-arhangelsk-sayt.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-arhangelsk-sayt.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12667,8 +12751,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12687,12 +12772,12 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-chita-lending.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-chita-lending.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12814,10 +12899,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12841,7 +12927,7 @@
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-kaluga-sayt.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-kaluga-sayt.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -12955,8 +13041,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -12975,12 +13062,12 @@
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-smolensk-vizitka.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-smolensk-vizitka.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13102,10 +13189,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13124,12 +13212,12 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-yakutsk-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-yakutsk-sayt.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13251,10 +13339,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13273,12 +13362,12 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-saransk-sayt.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-saransk-sayt.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13400,10 +13489,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13422,12 +13512,12 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-vologda-sayt.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-vologda-sayt.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13541,8 +13631,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13561,12 +13652,12 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-kurgan-lending.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-kurgan-lending.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13688,10 +13779,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13710,12 +13802,12 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-orel-sayt.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-orel-sayt.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13829,8 +13921,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13849,12 +13942,12 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-vladikavkaz-vizitka.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-vladikavkaz-vizitka.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -13976,10 +14069,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -13998,12 +14092,12 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-murmansk-sayt.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-murmansk-sayt.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14125,10 +14219,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -14147,12 +14242,12 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-tambov-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-tambov-sayt.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/17.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14274,10 +14369,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -14296,12 +14392,12 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-petrozavodsk-sayt.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-petrozavodsk-sayt.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/23.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14415,8 +14511,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -14435,12 +14532,12 @@
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-kostroma-lending.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-kostroma-lending.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/30.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14562,10 +14659,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -14584,12 +14682,12 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-yoshkar-ola-sayt.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-yoshkar-ola-sayt.jpg | https://ysddev.com/avito/w4/36.jpg | https://ysddev.com/avito/w4/37.jpg | https://ysddev.com/avito/w4/54.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/55.jpg | https://ysddev.com/avito/w4/24.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14703,8 +14801,9 @@
 • Удобно с телефона и готово под рекламу в Директе и соцсетях
 • Домен, хостинг, SSL и Яндекс Метрика с целями
 ЦЕНА И СРОК
-Лендинг или сайт-визитка — от 10 000 ₽, 1–2 дня
-Нужно больше страниц: сайт компании — от 14 990 ₽, 3–5 дней
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Нужно больше страниц: сайт компании — от 20 000 ₽, 3–5 дней
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Коротко рассказываете, что продаёте, — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -14723,12 +14822,12 @@
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-syktyvkar-vizitka.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-syktyvkar-vizitka.jpg | https://ysddev.com/avito/w4/31.jpg | https://ysddev.com/avito/w4/21.jpg | https://ysddev.com/avito/w4/26.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/20.jpg | https://ysddev.com/avito/w4/27.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
@@ -14850,10 +14949,11 @@
 • Сайт находят в Яндексе и Google: базовое SEO и Яндекс Метрика
 • Домен, хостинг и SSL подключу сам
 ЦЕНЫ И СРОКИ
-Сайт-визитка или лендинг — от 10 000 ₽, 1–2 дня
-Сайт компании до 6 страниц — от 14 990 ₽, 3–5 дней
-Интернет-магазин — от 19 990 ₽, 5–7 дней
-Доработка готового сайта — цену назову после просмотра
+Сайт-визитка — от 6 000 ₽, лендинг — от 8 000 ₽, 1–2 дня
+Сайт компании до 6 страниц — от 20 000 ₽, 3–5 дней
+Интернет-магазин — от 25 000 ₽, 5–7 дней
+Доработка готового сайта — от 2 000 ₽, мелкие правки в день обращения
+Акция: −20% на первый заказ и месяц бесплатных правок после запуска. Второй продукт в том же заказе (сайт + бот или презентация) — −30%.
 КАК РАБОТАЮ
 1. Пишете пару предложений о бизнесе — в тот же день называю цену и срок
 2. Делаю макет первого экрана — бесплатно
@@ -14877,7 +14977,7 @@
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>https://ysddev.com/avito/c3/ysd-novorossiysk-sayt.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-4p.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
+          <t>https://ysddev.com/avito/c5/ysd-novorossiysk-sayt.jpg | https://ysddev.com/avito/w4/25.jpg | https://ysddev.com/avito/w4/18.jpg | https://ysddev.com/avito/w4/19.jpg | https://ysddev.com/avito/sayt-5p.jpg | https://ysddev.com/avito/w4/28.jpg | https://ysddev.com/avito/w4/22.jpg | https://ysddev.com/avito/w4/29.jpg | https://ysddev.com/avito/sayt-2h.jpg | https://ysddev.com/avito/sayt-3h.jpg</t>
         </is>
       </c>
     </row>
